--- a/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
+++ b/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ark-Detailed-Design\hull-form\calcs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6E9773A-D872-49A6-84B4-26EED5605F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57266AC8-D9C6-45D2-B77E-DA983939FF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="2745" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="123">
   <si>
     <t>m</t>
   </si>
@@ -375,6 +375,36 @@
   </si>
   <si>
     <t>LB block waterplane area</t>
+  </si>
+  <si>
+    <t>HALF</t>
+  </si>
+  <si>
+    <t>FULL</t>
+  </si>
+  <si>
+    <t>HONG</t>
+  </si>
+  <si>
+    <t>Deadrise</t>
+  </si>
+  <si>
+    <t>degs</t>
+  </si>
+  <si>
+    <t>Vert rad</t>
+  </si>
+  <si>
+    <t>Bilge rad</t>
+  </si>
+  <si>
+    <t>PURE BLOCK</t>
+  </si>
+  <si>
+    <t>Cb</t>
+  </si>
+  <si>
+    <t>Loss</t>
   </si>
 </sst>
 </file>
@@ -384,7 +414,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,6 +517,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -719,7 +758,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -818,11 +857,25 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3791,18 +3844,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>81</v>
       </c>
@@ -3820,7 +3874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -3839,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -3858,12 +3912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -3880,11 +3929,8 @@
       <c r="E6" t="s">
         <v>0</v>
       </c>
-      <c r="G6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -3901,28 +3947,16 @@
       <c r="E7" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>86</v>
       </c>
       <c r="D8">
         <v>0.9</v>
       </c>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="74"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -3930,31 +3964,54 @@
         <f>D7-D8</f>
         <v>30.342000000000002</v>
       </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="L11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="M11" s="3">
+        <f>H18*I18*J18/2</f>
+        <v>32372.510399999996</v>
+      </c>
+      <c r="N11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="F12" s="77" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="76" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="F13" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>92</v>
       </c>
@@ -3971,20 +4028,42 @@
         <f>SUM(B14:D14)</f>
         <v>14304.445000000002</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="3">
+        <f>E14*2</f>
+        <v>28608.890000000003</v>
+      </c>
+      <c r="G14" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="76" t="s">
+      <c r="H14" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="76">
+      <c r="I14" s="74">
         <v>524</v>
       </c>
-      <c r="I14" s="76" t="s">
+      <c r="J14" s="74" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L14" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="M14" s="3">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>5</v>
+      </c>
+      <c r="P14" s="80">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="78" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>89</v>
       </c>
@@ -4001,20 +4080,39 @@
         <f>SUM(B15:D15)</f>
         <v>158.74699999999999</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="3"/>
+      <c r="G15" t="s">
         <v>93</v>
       </c>
-      <c r="G15" s="76" t="s">
+      <c r="H15" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="76" t="s">
+      <c r="I15" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="I15" s="76" t="s">
+      <c r="J15" s="74" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M15" s="3">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="80">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="79" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>90</v>
       </c>
@@ -4033,20 +4131,39 @@
         <f>2*D16</f>
         <v>26.303999999999998</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="3"/>
+      <c r="G16" t="s">
         <v>0</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>300</v>
       </c>
-      <c r="H16" s="3">
+      <c r="I16" s="3">
         <v>50</v>
       </c>
-      <c r="I16" s="3">
+      <c r="J16" s="3">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="M16" s="3">
+        <v>3</v>
+      </c>
+      <c r="N16" s="3">
+        <v>3</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0</v>
+      </c>
+      <c r="P16" s="80">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="78" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>91</v>
       </c>
@@ -4066,23 +4183,42 @@
         <f>2*D17</f>
         <v>15.72</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="3"/>
+      <c r="G17" t="s">
         <v>0</v>
       </c>
-      <c r="G17" s="3">
-        <f>G16*$H$14</f>
+      <c r="H17" s="3">
+        <f>H16*$I$14</f>
         <v>157200</v>
       </c>
-      <c r="H17" s="3">
-        <f>H16*$H$14</f>
+      <c r="I17" s="3">
+        <f>I16*$I$14</f>
         <v>26200</v>
       </c>
-      <c r="I17" s="3">
-        <f>I16*$H$14</f>
+      <c r="J17" s="3">
+        <f>J16*$I$14</f>
         <v>15720</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M17" s="3">
+        <v>29381</v>
+      </c>
+      <c r="N17" s="3">
+        <v>31624</v>
+      </c>
+      <c r="O17" s="3">
+        <v>30012</v>
+      </c>
+      <c r="P17" s="80">
+        <v>30507</v>
+      </c>
+      <c r="Q17" s="78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>94</v>
       </c>
@@ -4099,26 +4235,49 @@
         <v>2619.9289036800001</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" ref="E16:E19" si="1">SUM(B18:D18)</f>
+        <f t="shared" ref="E18" si="1">SUM(B18:D18)</f>
         <v>16410.426675839997</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="3">
+        <f>E18*2</f>
+        <v>32820.853351679994</v>
+      </c>
+      <c r="G18" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="75">
-        <f>G17/1000</f>
+      <c r="H18" s="3">
+        <f>H17/1000</f>
         <v>157.19999999999999</v>
       </c>
-      <c r="H18" s="75">
-        <f t="shared" ref="H18:I18" si="2">H17/1000</f>
+      <c r="I18" s="3">
+        <f t="shared" ref="I18:J18" si="2">I17/1000</f>
         <v>26.2</v>
       </c>
-      <c r="I18" s="75">
+      <c r="J18" s="3">
         <f t="shared" si="2"/>
         <v>15.72</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="M18" s="5">
+        <f>M17/$M$11</f>
+        <v>0.90759102822004201</v>
+      </c>
+      <c r="N18" s="5">
+        <f>N17/$M$11</f>
+        <v>0.97687820960588845</v>
+      </c>
+      <c r="O18" s="5">
+        <f>O17/$M$11</f>
+        <v>0.92708287461079952</v>
+      </c>
+      <c r="P18" s="5">
+        <f>P17/$M$11</f>
+        <v>0.94237362574142547</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>95</v>
       </c>
@@ -4138,9 +4297,32 @@
         <f>E14/E18</f>
         <v>0.87166807314397887</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="75" t="s">
+      <c r="F19" s="8">
+        <f>F14/F18</f>
+        <v>0.87166807314397887</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="M19" s="68">
+        <f>1-M18</f>
+        <v>9.2408971779957993E-2</v>
+      </c>
+      <c r="N19" s="68">
+        <f>1-N18</f>
+        <v>2.3121790394111552E-2</v>
+      </c>
+      <c r="O19" s="68">
+        <f>1-O18</f>
+        <v>7.2917125389200477E-2</v>
+      </c>
+      <c r="P19" s="68">
+        <f>1-P18</f>
+        <v>5.7626374258574531E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B20" s="3">
@@ -4153,26 +4335,30 @@
         <v>251.88900000000001</v>
       </c>
       <c r="E20" s="3">
-        <f>SUM(B20:D20)*2</f>
+        <f>SUM(B20:D20)</f>
+        <v>1958.4090000000001</v>
+      </c>
+      <c r="F20" s="3">
+        <f>E20*2</f>
         <v>3916.8180000000002</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B23" s="3">
-        <f>E14</f>
-        <v>14304.445000000002</v>
+        <f>F14</f>
+        <v>28608.890000000003</v>
       </c>
       <c r="C23" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>102</v>
       </c>
@@ -4182,33 +4368,36 @@
       <c r="C24" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>104</v>
       </c>
       <c r="B25" s="3">
-        <f>B24*E14</f>
-        <v>14733.578350000002</v>
+        <f>B24*B23</f>
+        <v>29467.156700000003</v>
       </c>
       <c r="C25" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="75" t="s">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B26" s="3">
-        <f>E20*B24/100</f>
+        <f>F20*B24/100</f>
         <v>40.343225400000001</v>
       </c>
       <c r="C26" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="75" t="s">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B27" s="3">
@@ -4219,12 +4408,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="75" t="s">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B28" s="3">
-        <f>E20/B27</f>
+        <f>F20/B27</f>
         <v>0.93800697837200364</v>
       </c>
     </row>

--- a/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
+++ b/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ark-Detailed-Design\hull-form\calcs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57266AC8-D9C6-45D2-B77E-DA983939FF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538AB626-6793-46BA-961C-12431CDF6212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="2745" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2325" yWindow="810" windowWidth="21600" windowHeight="13320" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="April 2011" sheetId="4" r:id="rId2"/>
     <sheet name="block coeff" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Wave BM" sheetId="3" r:id="rId4"/>
+    <sheet name="Shear" sheetId="5" r:id="rId5"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId6"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="163">
   <si>
     <t>m</t>
   </si>
@@ -405,16 +409,137 @@
   </si>
   <si>
     <t>Loss</t>
+  </si>
+  <si>
+    <t>IACS UR S11 — Vertical Wave Bending Moment</t>
+  </si>
+  <si>
+    <t>Noah's Ark vs Panamax Bulk Carrier</t>
+  </si>
+  <si>
+    <t>Formula:  Mw = k · C · L² · B · (Cb + 0.7) × 10⁻³  [kN·m]</t>
+  </si>
+  <si>
+    <t>k = 110 (hogging)  |  k = 190 (sagging)  |  C = wave coefficient = 10.75 − ((300−L)/100)^1.5  for 100 ≤ L ≤ 300m</t>
+  </si>
+  <si>
+    <t>INPUTS</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Noah's Ark</t>
+  </si>
+  <si>
+    <t>Panamax</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Length L (m)</t>
+  </si>
+  <si>
+    <t>Ark: 300 × 0.524m | Panamax: typical</t>
+  </si>
+  <si>
+    <t>Beam B (m)</t>
+  </si>
+  <si>
+    <t>Ark: 50 × 0.524m | Panamax: typical</t>
+  </si>
+  <si>
+    <t>Block coefficient Cb</t>
+  </si>
+  <si>
+    <t>Ark: CAD AR-003-20110418 | Panamax: typical</t>
+  </si>
+  <si>
+    <t>Draft T (m)</t>
+  </si>
+  <si>
+    <t>Ark: 15 cubits (Gen 7:20) | Panamax: typical</t>
+  </si>
+  <si>
+    <t>Wave coefficient C</t>
+  </si>
+  <si>
+    <t>IACS UR S11 — valid 100 ≤ L ≤ 300m</t>
+  </si>
+  <si>
+    <t>RESULTS</t>
+  </si>
+  <si>
+    <t>Mw Hogging (kN·m)</t>
+  </si>
+  <si>
+    <t>k=110</t>
+  </si>
+  <si>
+    <t>Mw Sagging (kN·m)</t>
+  </si>
+  <si>
+    <t>k=190</t>
+  </si>
+  <si>
+    <t>Mw Hogging (MN·m)</t>
+  </si>
+  <si>
+    <t>Mw Sagging (MN·m)</t>
+  </si>
+  <si>
+    <t>Source: IACS Unified Requirement S11 (Rev.7, 2022). Blue cells = inputs (edit freely).</t>
+  </si>
+  <si>
+    <t>IACS UR S11 — Vertical Wave Shear Force</t>
+  </si>
+  <si>
+    <t>Formula:  Vw = k · C · L · B · (Cb + 0.7) × 10⁻²  [kN]</t>
+  </si>
+  <si>
+    <t>k = 30 (positive/hogging shear)  |  k = 37 (negative/sagging shear)  |  C = wave coefficient (same as WBM sheet)</t>
+  </si>
+  <si>
+    <t>Maximum shear occurs at approx. quarter-length points — governs hull wall, bulkhead connections, and frame sizing at L/4.</t>
+  </si>
+  <si>
+    <t>INPUTS (linked from Wave Bending Moment sheet)</t>
+  </si>
+  <si>
+    <t>Vw Positive/Hogging (kN)</t>
+  </si>
+  <si>
+    <t>k=30</t>
+  </si>
+  <si>
+    <t>Vw Negative/Sagging (kN)</t>
+  </si>
+  <si>
+    <t>k=37</t>
+  </si>
+  <si>
+    <t>Vw Positive/Hogging (MN)</t>
+  </si>
+  <si>
+    <t>Vw Negative/Sagging (MN)</t>
+  </si>
+  <si>
+    <t>Source: IACS UR S11 (Rev.7, 2022). Green cells = linked from WBM sheet — edit inputs there.</t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,8 +651,55 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,6 +722,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCDCDC"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -758,7 +936,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -876,6 +1054,24 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -892,6 +1088,46 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Wave Bending Moment"/>
+      <sheetName val="Wave Shear Force"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="9">
+          <cell r="D9" t="str">
+            <v>Ark: 300 × 0.524m | Panamax: typical</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="D10" t="str">
+            <v>Ark: 50 × 0.524m | Panamax: typical</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="D11" t="str">
+            <v>Ark: CAD AR-003-20110418 | Panamax: typical</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="D13" t="str">
+            <v>IACS UR S11 — valid 100 ≤ L ≤ 300m</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4424,9 +4660,464 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B1" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="82" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="83" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="84" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="85" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="86" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="87" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="88">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="D9" s="88">
+        <v>225</v>
+      </c>
+      <c r="E9" s="89" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="87" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="88">
+        <v>26.2</v>
+      </c>
+      <c r="D10" s="88">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E10" s="89" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="88">
+        <v>0.87</v>
+      </c>
+      <c r="D11" s="88">
+        <v>0.83</v>
+      </c>
+      <c r="E11" s="89" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="87" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="88">
+        <v>7.86</v>
+      </c>
+      <c r="D12" s="88">
+        <v>14</v>
+      </c>
+      <c r="E12" s="89" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="87" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="90">
+        <f>10.75-((300-C9)/100)^1.5</f>
+        <v>9.0435549373038686</v>
+      </c>
+      <c r="D13" s="90">
+        <f>10.75-((300-D9)/100)^1.5</f>
+        <v>10.100480947161671</v>
+      </c>
+      <c r="E13" s="89" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="85" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="86"/>
+      <c r="C16" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="86" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" s="86" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="87" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="91">
+        <f>110*C13*C9^2*C10*(C11+0.7)*0.001</f>
+        <v>1011201.9384049438</v>
+      </c>
+      <c r="D17" s="91">
+        <f>110*D13*D9^2*D10*(D11+0.7)*0.001</f>
+        <v>2771067.3266218402</v>
+      </c>
+      <c r="E17" s="89" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="87" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="91">
+        <f>190*C13*C9^2*C10*(C11+0.7)*0.001</f>
+        <v>1746621.5299721758</v>
+      </c>
+      <c r="D18" s="91">
+        <f>190*D13*D9^2*D10*(D11+0.7)*0.001</f>
+        <v>4786389.0187104503</v>
+      </c>
+      <c r="E18" s="89" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="87" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="91">
+        <f>C17/1000</f>
+        <v>1011.2019384049438</v>
+      </c>
+      <c r="D19" s="91">
+        <f>D17/1000</f>
+        <v>2771.06732662184</v>
+      </c>
+      <c r="E19" s="89"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="87" t="s">
+        <v>148</v>
+      </c>
+      <c r="C20" s="91">
+        <f>C18/1000</f>
+        <v>1746.6215299721757</v>
+      </c>
+      <c r="D20" s="91">
+        <f>D18/1000</f>
+        <v>4786.3890187104498</v>
+      </c>
+      <c r="E20" s="89"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="84" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F62205B2-DF39-4187-86F9-AC56B85900EE}">
+  <dimension ref="B1:I22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="31.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B1" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="82" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="83" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="84" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="85" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="86" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="86" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="87" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="88">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="D10" s="88">
+        <v>225</v>
+      </c>
+      <c r="E10" s="92" t="str">
+        <f>'[1]Wave Bending Moment'!D9</f>
+        <v>Ark: 300 × 0.524m | Panamax: typical</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="87" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="88">
+        <v>26.2</v>
+      </c>
+      <c r="D11" s="88">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E11" s="92" t="str">
+        <f>'[1]Wave Bending Moment'!D10</f>
+        <v>Ark: 50 × 0.524m | Panamax: typical</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="88">
+        <v>0.87</v>
+      </c>
+      <c r="D12" s="88">
+        <v>0.83</v>
+      </c>
+      <c r="E12" s="92" t="str">
+        <f>'[1]Wave Bending Moment'!D11</f>
+        <v>Ark: CAD AR-003-20110418 | Panamax: typical</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="87" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="88">
+        <f>10.75-((300-C10)/100)^1.5</f>
+        <v>9.0435549373038686</v>
+      </c>
+      <c r="D13" s="88">
+        <f>10.75-((300-D10)/100)^1.5</f>
+        <v>10.100480947161671</v>
+      </c>
+      <c r="E13" s="92" t="str">
+        <f>'[1]Wave Bending Moment'!D13</f>
+        <v>IACS UR S11 — valid 100 ≤ L ≤ 300m</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="85" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="86"/>
+      <c r="C16" s="86" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" s="86" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" s="86" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="87" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="91">
+        <f>30*C13*C10*C11*(C12+0.7)*0.01</f>
+        <v>17543.40628738626</v>
+      </c>
+      <c r="D17" s="91">
+        <f>30*D13*D10*D11*(D12+0.7)*0.01</f>
+        <v>33588.69486814351</v>
+      </c>
+      <c r="E17" s="89" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="87" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" s="91">
+        <f>37*C13*C10*C11*(C12+0.7)*0.01</f>
+        <v>21636.867754443054</v>
+      </c>
+      <c r="D18" s="91">
+        <f>37*D13*D10*D11*(D12+0.7)*0.01</f>
+        <v>41426.057004043672</v>
+      </c>
+      <c r="E18" s="89" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="87" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19" s="91">
+        <f>C17/1000</f>
+        <v>17.543406287386262</v>
+      </c>
+      <c r="D19" s="91">
+        <f>D17/1000</f>
+        <v>33.588694868143513</v>
+      </c>
+      <c r="E19" s="89"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="87" t="s">
+        <v>160</v>
+      </c>
+      <c r="C20" s="91">
+        <f>C18/1000</f>
+        <v>21.636867754443053</v>
+      </c>
+      <c r="D20" s="91">
+        <f>D18/1000</f>
+        <v>41.42605700404367</v>
+      </c>
+      <c r="E20" s="89"/>
+      <c r="I20" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="84" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B6:E6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
+++ b/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ark-Detailed-Design\hull-form\calcs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538AB626-6793-46BA-961C-12431CDF6212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B091DF-14B1-453B-8A04-DE14F203339C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="810" windowWidth="21600" windowHeight="13320" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="April 2011" sheetId="4" r:id="rId2"/>
     <sheet name="block coeff" sheetId="2" r:id="rId3"/>
     <sheet name="Wave BM" sheetId="3" r:id="rId4"/>
-    <sheet name="Shear" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="Shear" sheetId="5" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="190">
   <si>
     <t>m</t>
   </si>
@@ -529,6 +530,87 @@
   </si>
   <si>
     <t>`</t>
+  </si>
+  <si>
+    <t>Hong 9</t>
+  </si>
+  <si>
+    <t>Hong 10</t>
+  </si>
+  <si>
+    <t>Hong 0</t>
+  </si>
+  <si>
+    <t>Hong 5</t>
+  </si>
+  <si>
+    <t>Hong</t>
+  </si>
+  <si>
+    <t>inch</t>
+  </si>
+  <si>
+    <t>SK Si</t>
+  </si>
+  <si>
+    <t>Norm SK</t>
+  </si>
+  <si>
+    <t>Struct Si</t>
+  </si>
+  <si>
+    <t>Roll Si</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>0.3575 </t>
+  </si>
+  <si>
+    <t>Mr average</t>
+  </si>
+  <si>
+    <t>worst stability, worst bow accel</t>
+  </si>
+  <si>
+    <t>accel and roll problems</t>
+  </si>
+  <si>
+    <t>similar to the Ark but weaker</t>
+  </si>
+  <si>
+    <t>too low, strength issues</t>
+  </si>
+  <si>
+    <t>strongest, worst accelerations</t>
+  </si>
+  <si>
+    <t>2nd to hull #5</t>
+  </si>
+  <si>
+    <t>worst vertical accel, 3rd weakest</t>
+  </si>
+  <si>
+    <t>weakest, extreme vert accel</t>
+  </si>
+  <si>
+    <t>top stability, 4th worst accel </t>
+  </si>
+  <si>
+    <t>more sedate version of #9 </t>
+  </si>
+  <si>
+    <t>nice comfort, bit below average</t>
+  </si>
+  <si>
+    <t>0.155 </t>
+  </si>
+  <si>
+    <t>best comfort, 2nd last the rest</t>
+  </si>
+  <si>
+    <t>Hull #</t>
   </si>
 </sst>
 </file>
@@ -537,9 +619,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -698,8 +780,47 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7.5"/>
+      <color rgb="FF990000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7.5"/>
+      <color rgb="FF990000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -730,8 +851,20 @@
         <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -931,12 +1064,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1050,10 +1237,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1062,16 +1255,33 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1088,6 +1298,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>180976</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>66762</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15DE1C40-FA86-51D7-72D7-C892C3C44F45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7724775" y="371476"/>
+          <a:ext cx="1828887" cy="2533649"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4292,7 +4568,7 @@
       <c r="O14" s="3">
         <v>5</v>
       </c>
-      <c r="P14" s="80">
+      <c r="P14" s="3">
         <v>3</v>
       </c>
       <c r="Q14" s="78" t="s">
@@ -4341,10 +4617,10 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="80">
+      <c r="P15" s="3">
         <v>2</v>
       </c>
-      <c r="Q15" s="79" t="s">
+      <c r="Q15" s="78" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4392,7 +4668,7 @@
       <c r="O16" s="3">
         <v>0</v>
       </c>
-      <c r="P16" s="80">
+      <c r="P16" s="3">
         <v>2</v>
       </c>
       <c r="Q16" s="78" t="s">
@@ -4447,7 +4723,7 @@
       <c r="O17" s="3">
         <v>30012</v>
       </c>
-      <c r="P17" s="80">
+      <c r="P17" s="3">
         <v>30507</v>
       </c>
       <c r="Q17" s="78" t="s">
@@ -4660,463 +4936,1391 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:E22"/>
+  <dimension ref="B1:M27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="39.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B1" s="81" t="s">
+    <row r="1" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B1" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+      <c r="I1" s="87"/>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="83" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="89" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="84" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="90" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="85" t="s">
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="80" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="86" t="s">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="81" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="86" t="s">
+      <c r="D8" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="81" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="87" t="s">
+      <c r="K8">
+        <v>9</v>
+      </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="88">
+      <c r="C9" s="83">
         <v>157.19999999999999</v>
       </c>
-      <c r="D9" s="88">
+      <c r="D9" s="83">
         <v>225</v>
       </c>
-      <c r="E9" s="89" t="s">
+      <c r="E9" s="83">
+        <v>135</v>
+      </c>
+      <c r="F9" s="83">
+        <v>90</v>
+      </c>
+      <c r="G9" s="83">
+        <v>112.5</v>
+      </c>
+      <c r="H9" s="83">
+        <v>90</v>
+      </c>
+      <c r="I9" s="79" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="87" t="s">
+      <c r="K9">
+        <f>F9/E9</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L9">
+        <f>G9/E9</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M9">
+        <f>H9/E9</f>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="88">
+      <c r="C10" s="83">
         <v>26.2</v>
       </c>
-      <c r="D10" s="88">
+      <c r="D10" s="83">
         <v>32.200000000000003</v>
       </c>
-      <c r="E10" s="89" t="s">
+      <c r="E10" s="83">
+        <v>22.5</v>
+      </c>
+      <c r="F10" s="83">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="G10" s="83">
+        <v>27</v>
+      </c>
+      <c r="H10" s="83">
+        <v>22.5</v>
+      </c>
+      <c r="I10" s="79" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="87" t="s">
+      <c r="K10">
+        <f>F10/E10</f>
+        <v>1.5022222222222221</v>
+      </c>
+      <c r="L10">
+        <f>G10/E10</f>
+        <v>1.2</v>
+      </c>
+      <c r="M10">
+        <f t="shared" ref="M10:M20" si="0">H10/E10</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="88">
+      <c r="C11" s="83">
         <v>0.87</v>
       </c>
-      <c r="D11" s="88">
+      <c r="D11" s="83">
         <v>0.83</v>
       </c>
-      <c r="E11" s="89" t="s">
+      <c r="E11" s="83">
+        <v>0.94</v>
+      </c>
+      <c r="F11" s="83">
+        <v>0.94</v>
+      </c>
+      <c r="G11" s="83">
+        <v>0.94</v>
+      </c>
+      <c r="H11" s="83">
+        <v>0.94</v>
+      </c>
+      <c r="I11" s="79" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="87" t="s">
+      <c r="K11">
+        <f>F11/E11</f>
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <f>G11/E11</f>
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="88">
+      <c r="C12" s="83">
         <v>7.86</v>
       </c>
-      <c r="D12" s="88">
+      <c r="D12" s="83">
         <v>14</v>
       </c>
-      <c r="E12" s="89" t="s">
+      <c r="E12" s="83">
+        <f>13.5/2</f>
+        <v>6.75</v>
+      </c>
+      <c r="F12" s="83">
+        <f>13.5/2</f>
+        <v>6.75</v>
+      </c>
+      <c r="G12" s="83">
+        <f t="shared" ref="G12" si="1">13.5/2</f>
+        <v>6.75</v>
+      </c>
+      <c r="H12" s="83">
+        <f>20.3/2</f>
+        <v>10.15</v>
+      </c>
+      <c r="I12" s="79" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="87" t="s">
+      <c r="K12">
+        <f>F12/E12</f>
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <f>G12/E12</f>
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="0"/>
+        <v>1.5037037037037038</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="82" t="s">
         <v>140</v>
       </c>
-      <c r="C13" s="90">
+      <c r="C13" s="84">
         <f>10.75-((300-C9)/100)^1.5</f>
         <v>9.0435549373038686</v>
       </c>
-      <c r="D13" s="90">
+      <c r="D13" s="84">
         <f>10.75-((300-D9)/100)^1.5</f>
         <v>10.100480947161671</v>
       </c>
-      <c r="E13" s="89" t="s">
+      <c r="E13" s="84">
+        <f>10.75-((300-E9)/100)^1.5</f>
+        <v>8.6305366245202535</v>
+      </c>
+      <c r="F13" s="84">
+        <f t="shared" ref="F13:H13" si="2">10.75-((300-F9)/100)^1.5</f>
+        <v>7.7068108833002178</v>
+      </c>
+      <c r="G13" s="84">
+        <f t="shared" si="2"/>
+        <v>8.182550511694533</v>
+      </c>
+      <c r="H13" s="84">
+        <f t="shared" si="2"/>
+        <v>7.7068108833002178</v>
+      </c>
+      <c r="I13" s="79" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="85" t="s">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="80" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="86"/>
-      <c r="C16" s="86" t="s">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="81"/>
+      <c r="C16" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="E16" s="86" t="s">
+      <c r="E16" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="I16" s="81" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="87" t="s">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="91">
+      <c r="C17" s="85">
         <f>110*C13*C9^2*C10*(C11+0.7)*0.001</f>
         <v>1011201.9384049438</v>
       </c>
-      <c r="D17" s="91">
+      <c r="D17" s="85">
         <f>110*D13*D9^2*D10*(D11+0.7)*0.001</f>
         <v>2771067.3266218402</v>
       </c>
-      <c r="E17" s="89" t="s">
+      <c r="E17" s="85">
+        <f t="shared" ref="E17:G17" si="3">110*E13*E9^2*E10*(E11+0.7)*0.001</f>
+        <v>638446.32019645744</v>
+      </c>
+      <c r="F17" s="85">
+        <f t="shared" si="3"/>
+        <v>380638.71132683998</v>
+      </c>
+      <c r="G17" s="85">
+        <f t="shared" si="3"/>
+        <v>504422.02025332808</v>
+      </c>
+      <c r="H17" s="85">
+        <f t="shared" ref="H17" si="4">110*H13*H9^2*H10*(H11+0.7)*0.001</f>
+        <v>253383.75754005619</v>
+      </c>
+      <c r="I17" s="79" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="87" t="s">
+      <c r="K17">
+        <f>F17/E17</f>
+        <v>0.59619532494088612</v>
+      </c>
+      <c r="L17">
+        <f>G17/E17</f>
+        <v>0.79007741809540311</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="0"/>
+        <v>0.39687558612928808</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="82" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="91">
+      <c r="C18" s="85">
         <f>190*C13*C9^2*C10*(C11+0.7)*0.001</f>
         <v>1746621.5299721758</v>
       </c>
-      <c r="D18" s="91">
+      <c r="D18" s="85">
         <f>190*D13*D9^2*D10*(D11+0.7)*0.001</f>
         <v>4786389.0187104503</v>
       </c>
-      <c r="E18" s="89" t="s">
+      <c r="E18" s="85">
+        <f t="shared" ref="E18:G18" si="5">190*E13*E9^2*E10*(E11+0.7)*0.001</f>
+        <v>1102770.916702972</v>
+      </c>
+      <c r="F18" s="85">
+        <f t="shared" si="5"/>
+        <v>657466.86501908721</v>
+      </c>
+      <c r="G18" s="85">
+        <f t="shared" si="5"/>
+        <v>871274.39861938485</v>
+      </c>
+      <c r="H18" s="85">
+        <f t="shared" ref="H18" si="6">190*H13*H9^2*H10*(H11+0.7)*0.001</f>
+        <v>437662.85393282439</v>
+      </c>
+      <c r="I18" s="79" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="87" t="s">
+      <c r="K18">
+        <f>F18/E18</f>
+        <v>0.59619532494088612</v>
+      </c>
+      <c r="L18">
+        <f>G18/E18</f>
+        <v>0.79007741809540299</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="0"/>
+        <v>0.39687558612928814</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B19" s="82" t="s">
         <v>147</v>
       </c>
-      <c r="C19" s="91">
+      <c r="C19" s="85">
         <f>C17/1000</f>
         <v>1011.2019384049438</v>
       </c>
-      <c r="D19" s="91">
+      <c r="D19" s="85">
         <f>D17/1000</f>
         <v>2771.06732662184</v>
       </c>
-      <c r="E19" s="89"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="87" t="s">
+      <c r="E19" s="85">
+        <f t="shared" ref="E19:G19" si="7">E17/1000</f>
+        <v>638.44632019645746</v>
+      </c>
+      <c r="F19" s="85">
+        <f t="shared" si="7"/>
+        <v>380.63871132684</v>
+      </c>
+      <c r="G19" s="85">
+        <f t="shared" si="7"/>
+        <v>504.42202025332807</v>
+      </c>
+      <c r="H19" s="85">
+        <f t="shared" ref="H19" si="8">H17/1000</f>
+        <v>253.38375754005619</v>
+      </c>
+      <c r="I19" s="79"/>
+      <c r="K19">
+        <f>F19/E19</f>
+        <v>0.59619532494088612</v>
+      </c>
+      <c r="L19">
+        <f>G19/E19</f>
+        <v>0.79007741809540299</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="0"/>
+        <v>0.39687558612928808</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B20" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="C20" s="91">
+      <c r="C20" s="85">
         <f>C18/1000</f>
         <v>1746.6215299721757</v>
       </c>
-      <c r="D20" s="91">
+      <c r="D20" s="85">
         <f>D18/1000</f>
         <v>4786.3890187104498</v>
       </c>
-      <c r="E20" s="89"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="84" t="s">
+      <c r="E20" s="85">
+        <f t="shared" ref="E20:G20" si="9">E18/1000</f>
+        <v>1102.770916702972</v>
+      </c>
+      <c r="F20" s="85">
+        <f t="shared" si="9"/>
+        <v>657.46686501908721</v>
+      </c>
+      <c r="G20" s="85">
+        <f t="shared" si="9"/>
+        <v>871.2743986193849</v>
+      </c>
+      <c r="H20" s="85">
+        <f t="shared" ref="H20" si="10">H18/1000</f>
+        <v>437.66285393282442</v>
+      </c>
+      <c r="I20" s="79"/>
+      <c r="K20">
+        <f>F20/E20</f>
+        <v>0.59619532494088601</v>
+      </c>
+      <c r="L20">
+        <f>G20/E20</f>
+        <v>0.79007741809540299</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="0"/>
+        <v>0.39687558612928814</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="90" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+      <c r="K22">
+        <f t="shared" ref="K22:L22" si="11">1/K20</f>
+        <v>1.6773026526149832</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="11"/>
+        <v>1.2656987493841376</v>
+      </c>
+      <c r="M22">
+        <f>1/M20</f>
+        <v>2.5196813181505076</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>17.5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25">
+        <f>E9/$C$27</f>
+        <v>300</v>
+      </c>
+      <c r="F25">
+        <f t="shared" ref="F25:H25" si="12">F9/$C$27</f>
+        <v>200</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="12"/>
+        <v>250</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="12"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <f>C25*25.4</f>
+        <v>444.5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <f t="shared" ref="E26:G27" si="13">E10/$C$27</f>
+        <v>50</v>
+      </c>
+      <c r="F26">
+        <f t="shared" ref="F26:H26" si="14">F10/$C$27</f>
+        <v>75.1111111111111</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="14"/>
+        <v>60</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="14"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C27">
+        <v>0.45</v>
+      </c>
+      <c r="D27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27">
+        <f>E12*2/$C$27</f>
+        <v>30</v>
+      </c>
+      <c r="F27">
+        <f t="shared" ref="F27:H27" si="15">F12*2/$C$27</f>
+        <v>30</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="15"/>
+        <v>30</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="15"/>
+        <v>45.111111111111114</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B22:I22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F61EFB5-6D33-40B3-B388-0C63A65D83F2}">
+  <dimension ref="B2:J15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="10" width="32.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="92" t="s">
+        <v>170</v>
+      </c>
+      <c r="H2" s="93" t="s">
+        <v>171</v>
+      </c>
+      <c r="I2" s="93" t="s">
+        <v>172</v>
+      </c>
+      <c r="J2" s="93" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="94">
+        <v>135</v>
+      </c>
+      <c r="C3" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D3" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E3" s="99">
+        <v>0</v>
+      </c>
+      <c r="F3" s="97" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" s="95">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H3" s="94">
+        <v>0.15</v>
+      </c>
+      <c r="I3" s="94">
+        <v>0.247</v>
+      </c>
+      <c r="J3" s="94" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="94">
+        <v>135</v>
+      </c>
+      <c r="C4" s="94">
+        <v>15</v>
+      </c>
+      <c r="D4" s="96">
+        <v>20.3</v>
+      </c>
+      <c r="E4" s="99">
+        <v>1</v>
+      </c>
+      <c r="F4" s="97">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="G4" s="95">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="H4" s="94">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="94">
+        <v>1</v>
+      </c>
+      <c r="J4" s="94" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="94">
+        <v>135</v>
+      </c>
+      <c r="C5" s="94">
+        <v>18.8</v>
+      </c>
+      <c r="D5" s="96">
+        <v>16.2</v>
+      </c>
+      <c r="E5" s="99">
+        <v>2</v>
+      </c>
+      <c r="F5" s="97">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="G5" s="95">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="H5" s="94">
+        <v>0.11</v>
+      </c>
+      <c r="I5" s="94">
+        <v>0.42</v>
+      </c>
+      <c r="J5" s="94" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="94">
+        <v>135</v>
+      </c>
+      <c r="C6" s="94">
+        <v>27</v>
+      </c>
+      <c r="D6" s="96">
+        <v>11.25</v>
+      </c>
+      <c r="E6" s="99">
+        <v>3</v>
+      </c>
+      <c r="F6" s="97">
+        <v>0.31125000000000003</v>
+      </c>
+      <c r="G6" s="95">
+        <v>0.308</v>
+      </c>
+      <c r="H6" s="94">
+        <v>0.2</v>
+      </c>
+      <c r="I6" s="94">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J6" s="94" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="94">
+        <v>135</v>
+      </c>
+      <c r="C7" s="94">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D7" s="96">
+        <v>9</v>
+      </c>
+      <c r="E7" s="99">
+        <v>4</v>
+      </c>
+      <c r="F7" s="97">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="G7" s="95">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H7" s="94">
+        <v>0.35</v>
+      </c>
+      <c r="I7" s="94">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="J7" s="94" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="94">
+        <v>90</v>
+      </c>
+      <c r="C8" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D8" s="96">
+        <v>20.3</v>
+      </c>
+      <c r="E8" s="99">
+        <v>5</v>
+      </c>
+      <c r="F8" s="97">
+        <v>0.66</v>
+      </c>
+      <c r="G8" s="95">
+        <v>1</v>
+      </c>
+      <c r="H8" s="94">
+        <v>0</v>
+      </c>
+      <c r="I8" s="94">
+        <v>0.222</v>
+      </c>
+      <c r="J8" s="94" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="94">
+        <v>112.5</v>
+      </c>
+      <c r="C9" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D9" s="96">
+        <v>16.2</v>
+      </c>
+      <c r="E9" s="99">
+        <v>6</v>
+      </c>
+      <c r="F9" s="97">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="G9" s="95">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="H9" s="94">
+        <v>0.05</v>
+      </c>
+      <c r="I9" s="94">
+        <v>0.193</v>
+      </c>
+      <c r="J9" s="94" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="94">
+        <v>162</v>
+      </c>
+      <c r="C10" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D10" s="96">
+        <v>11.3</v>
+      </c>
+      <c r="E10" s="99">
+        <v>7</v>
+      </c>
+      <c r="F10" s="97">
+        <v>0.22875000000000001</v>
+      </c>
+      <c r="G10" s="95">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="H10" s="94">
+        <v>0.4</v>
+      </c>
+      <c r="I10" s="94">
+        <v>0.35</v>
+      </c>
+      <c r="J10" s="94" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="94">
+        <v>202.5</v>
+      </c>
+      <c r="C11" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D11" s="96">
+        <v>9</v>
+      </c>
+      <c r="E11" s="99">
+        <v>8</v>
+      </c>
+      <c r="F11" s="97">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G11" s="95">
+        <v>0.374</v>
+      </c>
+      <c r="H11" s="94">
+        <v>1</v>
+      </c>
+      <c r="I11" s="94">
+        <v>0.499</v>
+      </c>
+      <c r="J11" s="94" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="94">
+        <v>90</v>
+      </c>
+      <c r="C12" s="94">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D12" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E12" s="99">
+        <v>9</v>
+      </c>
+      <c r="F12" s="97">
+        <v>0.45124999999999998</v>
+      </c>
+      <c r="G12" s="95">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="H12" s="94">
+        <v>0.05</v>
+      </c>
+      <c r="I12" s="94">
+        <v>0</v>
+      </c>
+      <c r="J12" s="94" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="94">
+        <v>112.5</v>
+      </c>
+      <c r="C13" s="94">
+        <v>27</v>
+      </c>
+      <c r="D13" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E13" s="99">
+        <v>10</v>
+      </c>
+      <c r="F13" s="97">
+        <v>0.45</v>
+      </c>
+      <c r="G13" s="95">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="H13" s="94">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I13" s="94">
+        <v>0.12</v>
+      </c>
+      <c r="J13" s="94" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="94">
+        <v>162</v>
+      </c>
+      <c r="C14" s="94">
+        <v>18.8</v>
+      </c>
+      <c r="D14" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E14" s="99">
+        <v>11</v>
+      </c>
+      <c r="F14" s="97">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="G14" s="95">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H14" s="94">
+        <v>0.27</v>
+      </c>
+      <c r="I14" s="94">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="J14" s="94" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="94">
+        <v>202.5</v>
+      </c>
+      <c r="C15" s="94">
+        <v>15</v>
+      </c>
+      <c r="D15" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E15" s="99">
+        <v>12</v>
+      </c>
+      <c r="F15" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="95">
+        <v>0</v>
+      </c>
+      <c r="H15" s="94">
+        <v>0.65</v>
+      </c>
+      <c r="I15" s="94">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J15" s="94" t="s">
+        <v>188</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F62205B2-DF39-4187-86F9-AC56B85900EE}">
-  <dimension ref="B1:I22"/>
+  <dimension ref="B1:L22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="45.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B1" s="81" t="s">
+    <row r="1" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B1" s="87" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="82" t="s">
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
+      <c r="H1" s="87"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="88" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="83" t="s">
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="89" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="84" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="90" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="84" t="s">
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="90" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="85" t="s">
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="80" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="86" t="s">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="81" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="86" t="s">
+      <c r="D9" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="86" t="s">
+      <c r="E9" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="G9" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="H9" s="81" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="87" t="s">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="88">
+      <c r="C10" s="83">
         <v>157.19999999999999</v>
       </c>
-      <c r="D10" s="88">
+      <c r="D10" s="83">
         <v>225</v>
       </c>
-      <c r="E10" s="92" t="str">
+      <c r="E10" s="83">
+        <f>'Wave BM'!E9</f>
+        <v>135</v>
+      </c>
+      <c r="F10" s="83">
+        <f>'Wave BM'!F9</f>
+        <v>90</v>
+      </c>
+      <c r="G10" s="83">
+        <f>'Wave BM'!G9</f>
+        <v>112.5</v>
+      </c>
+      <c r="H10" s="86" t="str">
         <f>'[1]Wave Bending Moment'!D9</f>
         <v>Ark: 300 × 0.524m | Panamax: typical</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="87" t="s">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="82" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="88">
+      <c r="C11" s="83">
         <v>26.2</v>
       </c>
-      <c r="D11" s="88">
+      <c r="D11" s="83">
         <v>32.200000000000003</v>
       </c>
-      <c r="E11" s="92" t="str">
+      <c r="E11" s="83">
+        <f>'Wave BM'!E10</f>
+        <v>22.5</v>
+      </c>
+      <c r="F11" s="83">
+        <f>'Wave BM'!F10</f>
+        <v>33.799999999999997</v>
+      </c>
+      <c r="G11" s="83">
+        <f>'Wave BM'!G10</f>
+        <v>27</v>
+      </c>
+      <c r="H11" s="86" t="str">
         <f>'[1]Wave Bending Moment'!D10</f>
         <v>Ark: 50 × 0.524m | Panamax: typical</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="87" t="s">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="88">
+      <c r="C12" s="83">
         <v>0.87</v>
       </c>
-      <c r="D12" s="88">
+      <c r="D12" s="83">
         <v>0.83</v>
       </c>
-      <c r="E12" s="92" t="str">
+      <c r="E12" s="83">
+        <f>'Wave BM'!E11</f>
+        <v>0.94</v>
+      </c>
+      <c r="F12" s="83">
+        <f>E12</f>
+        <v>0.94</v>
+      </c>
+      <c r="G12" s="83">
+        <f>F12</f>
+        <v>0.94</v>
+      </c>
+      <c r="H12" s="86" t="str">
         <f>'[1]Wave Bending Moment'!D11</f>
         <v>Ark: CAD AR-003-20110418 | Panamax: typical</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="87" t="s">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="82" t="s">
         <v>140</v>
       </c>
-      <c r="C13" s="88">
+      <c r="C13" s="83">
         <f>10.75-((300-C10)/100)^1.5</f>
         <v>9.0435549373038686</v>
       </c>
-      <c r="D13" s="88">
+      <c r="D13" s="83">
         <f>10.75-((300-D10)/100)^1.5</f>
         <v>10.100480947161671</v>
       </c>
-      <c r="E13" s="92" t="str">
+      <c r="E13" s="83">
+        <f>10.75-((300-E10)/100)^1.5</f>
+        <v>8.6305366245202535</v>
+      </c>
+      <c r="F13" s="83">
+        <f t="shared" ref="F13:G13" si="0">10.75-((300-F10)/100)^1.5</f>
+        <v>7.7068108833002178</v>
+      </c>
+      <c r="G13" s="83">
+        <f t="shared" si="0"/>
+        <v>8.182550511694533</v>
+      </c>
+      <c r="H13" s="86" t="str">
         <f>'[1]Wave Bending Moment'!D13</f>
         <v>IACS UR S11 — valid 100 ≤ L ≤ 300m</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="85" t="s">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="80" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="86"/>
-      <c r="C16" s="86" t="s">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="81"/>
+      <c r="C16" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="81" t="s">
         <v>130</v>
       </c>
-      <c r="E16" s="86" t="s">
+      <c r="E16" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="F16" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" s="81" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="87" t="s">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="82" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="91">
+      <c r="C17" s="85">
         <f>30*C13*C10*C11*(C12+0.7)*0.01</f>
         <v>17543.40628738626</v>
       </c>
-      <c r="D17" s="91">
+      <c r="D17" s="85">
         <f>30*D13*D10*D11*(D12+0.7)*0.01</f>
         <v>33588.69486814351</v>
       </c>
-      <c r="E17" s="89" t="s">
+      <c r="E17" s="85">
+        <f t="shared" ref="E17:G17" si="1">30*E13*E10*E11*(E12+0.7)*0.01</f>
+        <v>12897.905458514293</v>
+      </c>
+      <c r="F17" s="85">
+        <f t="shared" si="1"/>
+        <v>11534.506403843636</v>
+      </c>
+      <c r="G17" s="85">
+        <f t="shared" si="1"/>
+        <v>12228.412612201893</v>
+      </c>
+      <c r="H17" s="79" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="87" t="s">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="91">
+      <c r="C18" s="85">
         <f>37*C13*C10*C11*(C12+0.7)*0.01</f>
         <v>21636.867754443054</v>
       </c>
-      <c r="D18" s="91">
+      <c r="D18" s="85">
         <f>37*D13*D10*D11*(D12+0.7)*0.01</f>
         <v>41426.057004043672</v>
       </c>
-      <c r="E18" s="89" t="s">
+      <c r="E18" s="85">
+        <f t="shared" ref="E18:G18" si="2">37*E13*E10*E11*(E12+0.7)*0.01</f>
+        <v>15907.416732167627</v>
+      </c>
+      <c r="F18" s="85">
+        <f t="shared" si="2"/>
+        <v>14225.891231407149</v>
+      </c>
+      <c r="G18" s="85">
+        <f t="shared" si="2"/>
+        <v>15081.70888838234</v>
+      </c>
+      <c r="H18" s="79" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="87" t="s">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="C19" s="91">
+      <c r="C19" s="85">
         <f>C17/1000</f>
         <v>17.543406287386262</v>
       </c>
-      <c r="D19" s="91">
+      <c r="D19" s="85">
         <f>D17/1000</f>
         <v>33.588694868143513</v>
       </c>
-      <c r="E19" s="89"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="87" t="s">
+      <c r="E19" s="85">
+        <f t="shared" ref="E19:G19" si="3">E17/1000</f>
+        <v>12.897905458514293</v>
+      </c>
+      <c r="F19" s="85">
+        <f t="shared" si="3"/>
+        <v>11.534506403843636</v>
+      </c>
+      <c r="G19" s="85">
+        <f t="shared" si="3"/>
+        <v>12.228412612201893</v>
+      </c>
+      <c r="H19" s="79"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="C20" s="91">
+      <c r="C20" s="85">
         <f>C18/1000</f>
         <v>21.636867754443053</v>
       </c>
-      <c r="D20" s="91">
+      <c r="D20" s="85">
         <f>D18/1000</f>
         <v>41.42605700404367</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="I20" t="s">
+      <c r="E20" s="85">
+        <f t="shared" ref="E20:G20" si="4">E18/1000</f>
+        <v>15.907416732167627</v>
+      </c>
+      <c r="F20" s="85">
+        <f t="shared" si="4"/>
+        <v>14.22589123140715</v>
+      </c>
+      <c r="G20" s="85">
+        <f t="shared" si="4"/>
+        <v>15.081708888382339</v>
+      </c>
+      <c r="H20" s="79"/>
+      <c r="L20" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="84" t="s">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="90" t="s">
         <v>161</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
+      <c r="H22" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
+++ b/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ark-Detailed-Design\hull-form\calcs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B091DF-14B1-453B-8A04-DE14F203339C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD030B5-DA7F-40CD-A300-6DF14AAFCF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="615" windowWidth="21600" windowHeight="14715" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="210">
   <si>
     <t>m</t>
   </si>
@@ -611,6 +611,127 @@
   </si>
   <si>
     <t>Hull #</t>
+  </si>
+  <si>
+    <t>SEAKEEPING</t>
+  </si>
+  <si>
+    <t>STRENGTH</t>
+  </si>
+  <si>
+    <t>ROLL STABILITY</t>
+  </si>
+  <si>
+    <t>REC</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>GZ</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>Ship No.</t>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>lim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (degree)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (m</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rad)</t>
+    </r>
+  </si>
+  <si>
+    <t>CHECK</t>
+  </si>
+  <si>
+    <t>Heel</t>
+  </si>
+  <si>
+    <t>AutoCad</t>
+  </si>
+  <si>
+    <t>Vb calc</t>
+  </si>
+  <si>
+    <t>JS calc</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>Vol</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Disp</t>
+  </si>
+  <si>
+    <t>Cb 0.87</t>
   </si>
 </sst>
 </file>
@@ -621,7 +742,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -819,8 +940,35 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Symbol"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -863,8 +1011,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1096,6 +1262,17 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -1118,12 +1295,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1270,10 +1518,10 @@
     <xf numFmtId="0" fontId="28" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1281,6 +1529,141 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1305,15 +1688,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
+      <xdr:colOff>11113</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>66762</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>416012</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1343,8 +1726,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7724775" y="371476"/>
-          <a:ext cx="1828887" cy="2533649"/>
+          <a:off x="7686676" y="3411538"/>
+          <a:ext cx="1833649" cy="2533649"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4857,6 +5240,30 @@
       <c r="G20" t="s">
         <v>107</v>
       </c>
+      <c r="I20" t="s">
+        <v>206</v>
+      </c>
+      <c r="J20">
+        <f>H18*I18*J18</f>
+        <v>64745.020799999991</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I21" t="s">
+        <v>207</v>
+      </c>
+      <c r="J21">
+        <v>1.0249999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>208</v>
+      </c>
+      <c r="J22">
+        <f>J20*J21/2</f>
+        <v>33181.823159999993</v>
+      </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
@@ -4868,6 +5275,13 @@
       </c>
       <c r="C23" t="s">
         <v>88</v>
+      </c>
+      <c r="I23" t="s">
+        <v>209</v>
+      </c>
+      <c r="J23">
+        <f>J22*0.87</f>
+        <v>28868.186149199992</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -5542,10 +5956,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F61EFB5-6D33-40B3-B388-0C63A65D83F2}">
-  <dimension ref="B2:J15"/>
+  <dimension ref="B2:T78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="32.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
@@ -5578,31 +5993,31 @@
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="94">
+      <c r="B3" s="129">
         <v>135</v>
       </c>
-      <c r="C3" s="94">
+      <c r="C3" s="129">
         <v>22.5</v>
       </c>
-      <c r="D3" s="96">
+      <c r="D3" s="130">
         <v>13.5</v>
       </c>
-      <c r="E3" s="99">
+      <c r="E3" s="131">
         <v>0</v>
       </c>
-      <c r="F3" s="97" t="s">
+      <c r="F3" s="132" t="s">
         <v>174</v>
       </c>
-      <c r="G3" s="95">
+      <c r="G3" s="133">
         <v>0.39900000000000002</v>
       </c>
-      <c r="H3" s="94">
+      <c r="H3" s="129">
         <v>0.15</v>
       </c>
-      <c r="I3" s="94">
+      <c r="I3" s="129">
         <v>0.247</v>
       </c>
-      <c r="J3" s="94" t="s">
+      <c r="J3" s="129" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5723,31 +6138,31 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="94">
+      <c r="B8" s="100">
         <v>90</v>
       </c>
-      <c r="C8" s="94">
+      <c r="C8" s="100">
         <v>22.5</v>
       </c>
-      <c r="D8" s="96">
+      <c r="D8" s="101">
         <v>20.3</v>
       </c>
-      <c r="E8" s="99">
+      <c r="E8" s="102">
         <v>5</v>
       </c>
-      <c r="F8" s="97">
+      <c r="F8" s="103">
         <v>0.66</v>
       </c>
-      <c r="G8" s="95">
+      <c r="G8" s="104">
         <v>1</v>
       </c>
-      <c r="H8" s="94">
+      <c r="H8" s="100">
         <v>0</v>
       </c>
-      <c r="I8" s="94">
+      <c r="I8" s="100">
         <v>0.222</v>
       </c>
-      <c r="J8" s="94" t="s">
+      <c r="J8" s="100" t="s">
         <v>180</v>
       </c>
     </row>
@@ -5839,31 +6254,31 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="94">
+      <c r="B12" s="105">
         <v>90</v>
       </c>
-      <c r="C12" s="94">
+      <c r="C12" s="105">
         <v>33.799999999999997</v>
       </c>
-      <c r="D12" s="96">
+      <c r="D12" s="106">
         <v>13.5</v>
       </c>
-      <c r="E12" s="99">
+      <c r="E12" s="107">
         <v>9</v>
       </c>
-      <c r="F12" s="97">
+      <c r="F12" s="108">
         <v>0.45124999999999998</v>
       </c>
-      <c r="G12" s="95">
+      <c r="G12" s="109">
         <v>0.58399999999999996</v>
       </c>
-      <c r="H12" s="94">
+      <c r="H12" s="105">
         <v>0.05</v>
       </c>
-      <c r="I12" s="94">
+      <c r="I12" s="105">
         <v>0</v>
       </c>
-      <c r="J12" s="94" t="s">
+      <c r="J12" s="105" t="s">
         <v>184</v>
       </c>
     </row>
@@ -5954,7 +6369,1720 @@
         <v>188</v>
       </c>
     </row>
+    <row r="17" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="24" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="F18" s="121" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" s="125" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18" s="111" t="s">
+        <v>171</v>
+      </c>
+      <c r="I18" s="93" t="s">
+        <v>172</v>
+      </c>
+      <c r="J18" s="93" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="94">
+        <v>202.5</v>
+      </c>
+      <c r="C19" s="94">
+        <v>15</v>
+      </c>
+      <c r="D19" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E19" s="99">
+        <v>12</v>
+      </c>
+      <c r="F19" s="122" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="126">
+        <v>0</v>
+      </c>
+      <c r="H19" s="97">
+        <v>0.65</v>
+      </c>
+      <c r="I19" s="94">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J19" s="94" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="94">
+        <v>162</v>
+      </c>
+      <c r="C20" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D20" s="96">
+        <v>11.3</v>
+      </c>
+      <c r="E20" s="99">
+        <v>7</v>
+      </c>
+      <c r="F20" s="122">
+        <v>0.22875000000000001</v>
+      </c>
+      <c r="G20" s="126">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="H20" s="97">
+        <v>0.4</v>
+      </c>
+      <c r="I20" s="94">
+        <v>0.35</v>
+      </c>
+      <c r="J20" s="94" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="94">
+        <v>135</v>
+      </c>
+      <c r="C21" s="94">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D21" s="96">
+        <v>9</v>
+      </c>
+      <c r="E21" s="99">
+        <v>4</v>
+      </c>
+      <c r="F21" s="122">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="G21" s="126">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H21" s="97">
+        <v>0.35</v>
+      </c>
+      <c r="I21" s="94">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="J21" s="94" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="94">
+        <v>162</v>
+      </c>
+      <c r="C22" s="94">
+        <v>18.8</v>
+      </c>
+      <c r="D22" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E22" s="99">
+        <v>11</v>
+      </c>
+      <c r="F22" s="122">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="G22" s="126">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H22" s="97">
+        <v>0.27</v>
+      </c>
+      <c r="I22" s="94">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="J22" s="94" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="94">
+        <v>135</v>
+      </c>
+      <c r="C23" s="94">
+        <v>27</v>
+      </c>
+      <c r="D23" s="96">
+        <v>11.25</v>
+      </c>
+      <c r="E23" s="99">
+        <v>3</v>
+      </c>
+      <c r="F23" s="122">
+        <v>0.31125000000000003</v>
+      </c>
+      <c r="G23" s="126">
+        <v>0.308</v>
+      </c>
+      <c r="H23" s="97">
+        <v>0.2</v>
+      </c>
+      <c r="I23" s="94">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J23" s="94" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="94">
+        <v>202.5</v>
+      </c>
+      <c r="C24" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D24" s="96">
+        <v>9</v>
+      </c>
+      <c r="E24" s="99">
+        <v>8</v>
+      </c>
+      <c r="F24" s="122">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G24" s="126">
+        <v>0.374</v>
+      </c>
+      <c r="H24" s="97">
+        <v>1</v>
+      </c>
+      <c r="I24" s="94">
+        <v>0.499</v>
+      </c>
+      <c r="J24" s="94" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="129">
+        <v>135</v>
+      </c>
+      <c r="C25" s="129">
+        <v>22.5</v>
+      </c>
+      <c r="D25" s="130">
+        <v>13.5</v>
+      </c>
+      <c r="E25" s="131">
+        <v>0</v>
+      </c>
+      <c r="F25" s="134" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" s="135">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H25" s="132">
+        <v>0.15</v>
+      </c>
+      <c r="I25" s="129">
+        <v>0.247</v>
+      </c>
+      <c r="J25" s="129" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="94">
+        <v>135</v>
+      </c>
+      <c r="C26" s="94">
+        <v>15</v>
+      </c>
+      <c r="D26" s="96">
+        <v>20.3</v>
+      </c>
+      <c r="E26" s="99">
+        <v>1</v>
+      </c>
+      <c r="F26" s="122">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="G26" s="126">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="H26" s="97">
+        <v>0.1</v>
+      </c>
+      <c r="I26" s="94">
+        <v>1</v>
+      </c>
+      <c r="J26" s="94" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="94">
+        <v>112.5</v>
+      </c>
+      <c r="C27" s="94">
+        <v>27</v>
+      </c>
+      <c r="D27" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E27" s="99">
+        <v>10</v>
+      </c>
+      <c r="F27" s="122">
+        <v>0.45</v>
+      </c>
+      <c r="G27" s="126">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="H27" s="97">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I27" s="94">
+        <v>0.12</v>
+      </c>
+      <c r="J27" s="94" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="105">
+        <v>90</v>
+      </c>
+      <c r="C28" s="105">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D28" s="106">
+        <v>13.5</v>
+      </c>
+      <c r="E28" s="107">
+        <v>9</v>
+      </c>
+      <c r="F28" s="123">
+        <v>0.45124999999999998</v>
+      </c>
+      <c r="G28" s="127">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="H28" s="108">
+        <v>0.05</v>
+      </c>
+      <c r="I28" s="105">
+        <v>0</v>
+      </c>
+      <c r="J28" s="105" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="94">
+        <v>135</v>
+      </c>
+      <c r="C29" s="94">
+        <v>18.8</v>
+      </c>
+      <c r="D29" s="96">
+        <v>16.2</v>
+      </c>
+      <c r="E29" s="99">
+        <v>2</v>
+      </c>
+      <c r="F29" s="122">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="G29" s="126">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="H29" s="97">
+        <v>0.11</v>
+      </c>
+      <c r="I29" s="94">
+        <v>0.42</v>
+      </c>
+      <c r="J29" s="94" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="94">
+        <v>112.5</v>
+      </c>
+      <c r="C30" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D30" s="96">
+        <v>16.2</v>
+      </c>
+      <c r="E30" s="99">
+        <v>6</v>
+      </c>
+      <c r="F30" s="122">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="G30" s="126">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="H30" s="97">
+        <v>0.05</v>
+      </c>
+      <c r="I30" s="94">
+        <v>0.193</v>
+      </c>
+      <c r="J30" s="94" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="100">
+        <v>90</v>
+      </c>
+      <c r="C31" s="100">
+        <v>22.5</v>
+      </c>
+      <c r="D31" s="101">
+        <v>20.3</v>
+      </c>
+      <c r="E31" s="102">
+        <v>5</v>
+      </c>
+      <c r="F31" s="124">
+        <v>0.66</v>
+      </c>
+      <c r="G31" s="128">
+        <v>1</v>
+      </c>
+      <c r="H31" s="103">
+        <v>0</v>
+      </c>
+      <c r="I31" s="100">
+        <v>0.222</v>
+      </c>
+      <c r="J31" s="100" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B34" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="G34" s="117" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="I34" s="111" t="s">
+        <v>172</v>
+      </c>
+      <c r="J34" s="93" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B35" s="100">
+        <v>90</v>
+      </c>
+      <c r="C35" s="100">
+        <v>22.5</v>
+      </c>
+      <c r="D35" s="101">
+        <v>20.3</v>
+      </c>
+      <c r="E35" s="102">
+        <v>5</v>
+      </c>
+      <c r="F35" s="103">
+        <v>0.66</v>
+      </c>
+      <c r="G35" s="118">
+        <v>1</v>
+      </c>
+      <c r="H35" s="115">
+        <v>0</v>
+      </c>
+      <c r="I35" s="103">
+        <v>0.222</v>
+      </c>
+      <c r="J35" s="100" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B36" s="94">
+        <v>112.5</v>
+      </c>
+      <c r="C36" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D36" s="96">
+        <v>16.2</v>
+      </c>
+      <c r="E36" s="99">
+        <v>6</v>
+      </c>
+      <c r="F36" s="97">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="G36" s="119">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="H36" s="114">
+        <v>0.05</v>
+      </c>
+      <c r="I36" s="97">
+        <v>0.193</v>
+      </c>
+      <c r="J36" s="94" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B37" s="105">
+        <v>90</v>
+      </c>
+      <c r="C37" s="105">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D37" s="106">
+        <v>13.5</v>
+      </c>
+      <c r="E37" s="107">
+        <v>9</v>
+      </c>
+      <c r="F37" s="108">
+        <v>0.45124999999999998</v>
+      </c>
+      <c r="G37" s="120">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="H37" s="113">
+        <v>0.05</v>
+      </c>
+      <c r="I37" s="108">
+        <v>0</v>
+      </c>
+      <c r="J37" s="105" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B38" s="94">
+        <v>112.5</v>
+      </c>
+      <c r="C38" s="94">
+        <v>27</v>
+      </c>
+      <c r="D38" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E38" s="99">
+        <v>10</v>
+      </c>
+      <c r="F38" s="97">
+        <v>0.45</v>
+      </c>
+      <c r="G38" s="119">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="H38" s="114">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I38" s="97">
+        <v>0.12</v>
+      </c>
+      <c r="J38" s="94" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B39" s="94">
+        <v>135</v>
+      </c>
+      <c r="C39" s="94">
+        <v>15</v>
+      </c>
+      <c r="D39" s="96">
+        <v>20.3</v>
+      </c>
+      <c r="E39" s="99">
+        <v>1</v>
+      </c>
+      <c r="F39" s="97">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="G39" s="119">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="H39" s="114">
+        <v>0.1</v>
+      </c>
+      <c r="I39" s="97">
+        <v>1</v>
+      </c>
+      <c r="J39" s="94" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B40" s="94">
+        <v>135</v>
+      </c>
+      <c r="C40" s="94">
+        <v>18.8</v>
+      </c>
+      <c r="D40" s="96">
+        <v>16.2</v>
+      </c>
+      <c r="E40" s="99">
+        <v>2</v>
+      </c>
+      <c r="F40" s="97">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="G40" s="119">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="H40" s="114">
+        <v>0.11</v>
+      </c>
+      <c r="I40" s="97">
+        <v>0.42</v>
+      </c>
+      <c r="J40" s="94" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" s="129">
+        <v>135</v>
+      </c>
+      <c r="C41" s="129">
+        <v>22.5</v>
+      </c>
+      <c r="D41" s="130">
+        <v>13.5</v>
+      </c>
+      <c r="E41" s="131">
+        <v>0</v>
+      </c>
+      <c r="F41" s="132" t="s">
+        <v>174</v>
+      </c>
+      <c r="G41" s="136">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H41" s="137">
+        <v>0.15</v>
+      </c>
+      <c r="I41" s="132">
+        <v>0.247</v>
+      </c>
+      <c r="J41" s="129" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" s="94">
+        <v>135</v>
+      </c>
+      <c r="C42" s="94">
+        <v>27</v>
+      </c>
+      <c r="D42" s="96">
+        <v>11.25</v>
+      </c>
+      <c r="E42" s="99">
+        <v>3</v>
+      </c>
+      <c r="F42" s="97">
+        <v>0.31125000000000003</v>
+      </c>
+      <c r="G42" s="119">
+        <v>0.308</v>
+      </c>
+      <c r="H42" s="114">
+        <v>0.2</v>
+      </c>
+      <c r="I42" s="97">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J42" s="94" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B43" s="94">
+        <v>162</v>
+      </c>
+      <c r="C43" s="94">
+        <v>18.8</v>
+      </c>
+      <c r="D43" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E43" s="99">
+        <v>11</v>
+      </c>
+      <c r="F43" s="97">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="G43" s="119">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H43" s="114">
+        <v>0.27</v>
+      </c>
+      <c r="I43" s="97">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="J43" s="94" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="94">
+        <v>135</v>
+      </c>
+      <c r="C44" s="94">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D44" s="96">
+        <v>9</v>
+      </c>
+      <c r="E44" s="99">
+        <v>4</v>
+      </c>
+      <c r="F44" s="97">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="G44" s="119">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H44" s="114">
+        <v>0.35</v>
+      </c>
+      <c r="I44" s="97">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="J44" s="94" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B45" s="94">
+        <v>162</v>
+      </c>
+      <c r="C45" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D45" s="96">
+        <v>11.3</v>
+      </c>
+      <c r="E45" s="99">
+        <v>7</v>
+      </c>
+      <c r="F45" s="97">
+        <v>0.22875000000000001</v>
+      </c>
+      <c r="G45" s="119">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="H45" s="114">
+        <v>0.4</v>
+      </c>
+      <c r="I45" s="97">
+        <v>0.35</v>
+      </c>
+      <c r="J45" s="94" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B46" s="94">
+        <v>202.5</v>
+      </c>
+      <c r="C46" s="94">
+        <v>15</v>
+      </c>
+      <c r="D46" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E46" s="99">
+        <v>12</v>
+      </c>
+      <c r="F46" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="G46" s="119">
+        <v>0</v>
+      </c>
+      <c r="H46" s="114">
+        <v>0.65</v>
+      </c>
+      <c r="I46" s="97">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J46" s="94" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="94">
+        <v>202.5</v>
+      </c>
+      <c r="C47" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D47" s="96">
+        <v>9</v>
+      </c>
+      <c r="E47" s="99">
+        <v>8</v>
+      </c>
+      <c r="F47" s="97">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G47" s="119">
+        <v>0.374</v>
+      </c>
+      <c r="H47" s="116">
+        <v>1</v>
+      </c>
+      <c r="I47" s="97">
+        <v>0.499</v>
+      </c>
+      <c r="J47" s="94" t="s">
+        <v>183</v>
+      </c>
+      <c r="M47" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" t="s">
+        <v>167</v>
+      </c>
+      <c r="O47" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M48" s="3">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="O48" s="9">
+        <f>M48/N48</f>
+        <v>1.1644444444444444</v>
+      </c>
+    </row>
+    <row r="49" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="24" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="50" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B50" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="F50" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="G50" s="92" t="s">
+        <v>170</v>
+      </c>
+      <c r="H50" s="110" t="s">
+        <v>171</v>
+      </c>
+      <c r="I50" s="112" t="s">
+        <v>172</v>
+      </c>
+      <c r="J50" s="111" t="s">
+        <v>173</v>
+      </c>
+      <c r="L50" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="M50" s="91" t="s">
+        <v>90</v>
+      </c>
+      <c r="N50" s="91" t="s">
+        <v>91</v>
+      </c>
+      <c r="O50" s="98" t="s">
+        <v>189</v>
+      </c>
+      <c r="P50" s="140" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B51" s="129">
+        <v>135</v>
+      </c>
+      <c r="C51" s="129">
+        <v>22.5</v>
+      </c>
+      <c r="D51" s="130">
+        <v>13.5</v>
+      </c>
+      <c r="E51" s="131">
+        <v>0</v>
+      </c>
+      <c r="F51" s="132" t="s">
+        <v>174</v>
+      </c>
+      <c r="G51" s="133">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H51" s="130">
+        <v>0.15</v>
+      </c>
+      <c r="I51" s="137">
+        <v>0.247</v>
+      </c>
+      <c r="J51" s="132" t="s">
+        <v>175</v>
+      </c>
+      <c r="L51" s="138">
+        <f>B51*$O$48</f>
+        <v>157.19999999999999</v>
+      </c>
+      <c r="M51" s="138">
+        <f>C51*$O$48</f>
+        <v>26.2</v>
+      </c>
+      <c r="N51" s="138">
+        <f>D51*$O$48</f>
+        <v>15.719999999999999</v>
+      </c>
+      <c r="O51" s="139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B52" s="94">
+        <v>135</v>
+      </c>
+      <c r="C52" s="94">
+        <v>15</v>
+      </c>
+      <c r="D52" s="96">
+        <v>20.3</v>
+      </c>
+      <c r="E52" s="99">
+        <v>1</v>
+      </c>
+      <c r="F52" s="97">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="G52" s="95">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="H52" s="96">
+        <v>0.1</v>
+      </c>
+      <c r="I52" s="114">
+        <v>1</v>
+      </c>
+      <c r="J52" s="97" t="s">
+        <v>176</v>
+      </c>
+      <c r="L52" s="138">
+        <f t="shared" ref="L52:L63" si="0">B52*$O$48</f>
+        <v>157.19999999999999</v>
+      </c>
+      <c r="M52" s="138">
+        <f t="shared" ref="M52:M63" si="1">C52*$O$48</f>
+        <v>17.466666666666665</v>
+      </c>
+      <c r="N52" s="138">
+        <f t="shared" ref="N52:N63" si="2">D52*$O$48</f>
+        <v>23.638222222222222</v>
+      </c>
+      <c r="O52" s="139">
+        <v>1</v>
+      </c>
+      <c r="T52" s="20"/>
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B53" s="94">
+        <v>135</v>
+      </c>
+      <c r="C53" s="94">
+        <v>18.8</v>
+      </c>
+      <c r="D53" s="96">
+        <v>16.2</v>
+      </c>
+      <c r="E53" s="99">
+        <v>2</v>
+      </c>
+      <c r="F53" s="97">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="G53" s="95">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="H53" s="96">
+        <v>0.11</v>
+      </c>
+      <c r="I53" s="114">
+        <v>0.42</v>
+      </c>
+      <c r="J53" s="97" t="s">
+        <v>177</v>
+      </c>
+      <c r="L53" s="138">
+        <f t="shared" si="0"/>
+        <v>157.19999999999999</v>
+      </c>
+      <c r="M53" s="138">
+        <f t="shared" si="1"/>
+        <v>21.891555555555556</v>
+      </c>
+      <c r="N53" s="138">
+        <f t="shared" si="2"/>
+        <v>18.863999999999997</v>
+      </c>
+      <c r="O53" s="139">
+        <v>2</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="T53" s="3"/>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B54" s="94">
+        <v>135</v>
+      </c>
+      <c r="C54" s="94">
+        <v>27</v>
+      </c>
+      <c r="D54" s="96">
+        <v>11.25</v>
+      </c>
+      <c r="E54" s="99">
+        <v>3</v>
+      </c>
+      <c r="F54" s="97">
+        <v>0.31125000000000003</v>
+      </c>
+      <c r="G54" s="95">
+        <v>0.308</v>
+      </c>
+      <c r="H54" s="96">
+        <v>0.2</v>
+      </c>
+      <c r="I54" s="114">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J54" s="97" t="s">
+        <v>178</v>
+      </c>
+      <c r="L54" s="138">
+        <f t="shared" si="0"/>
+        <v>157.19999999999999</v>
+      </c>
+      <c r="M54" s="138">
+        <f t="shared" si="1"/>
+        <v>31.439999999999998</v>
+      </c>
+      <c r="N54" s="138">
+        <f t="shared" si="2"/>
+        <v>13.1</v>
+      </c>
+      <c r="O54" s="139">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="S54" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B55" s="94">
+        <v>135</v>
+      </c>
+      <c r="C55" s="94">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D55" s="96">
+        <v>9</v>
+      </c>
+      <c r="E55" s="99">
+        <v>4</v>
+      </c>
+      <c r="F55" s="97">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="G55" s="95">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H55" s="96">
+        <v>0.35</v>
+      </c>
+      <c r="I55" s="114">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="J55" s="97" t="s">
+        <v>179</v>
+      </c>
+      <c r="L55" s="138">
+        <f t="shared" si="0"/>
+        <v>157.19999999999999</v>
+      </c>
+      <c r="M55" s="138">
+        <f t="shared" si="1"/>
+        <v>39.358222222222217</v>
+      </c>
+      <c r="N55" s="138">
+        <f t="shared" si="2"/>
+        <v>10.48</v>
+      </c>
+      <c r="O55" s="139">
+        <v>4</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="S55" s="3">
+        <v>30</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B56" s="100">
+        <v>90</v>
+      </c>
+      <c r="C56" s="100">
+        <v>22.5</v>
+      </c>
+      <c r="D56" s="101">
+        <v>20.3</v>
+      </c>
+      <c r="E56" s="102">
+        <v>5</v>
+      </c>
+      <c r="F56" s="103">
+        <v>0.66</v>
+      </c>
+      <c r="G56" s="104">
+        <v>1</v>
+      </c>
+      <c r="H56" s="101">
+        <v>0</v>
+      </c>
+      <c r="I56" s="115">
+        <v>0.222</v>
+      </c>
+      <c r="J56" s="103" t="s">
+        <v>180</v>
+      </c>
+      <c r="L56" s="138">
+        <f t="shared" si="0"/>
+        <v>104.8</v>
+      </c>
+      <c r="M56" s="138">
+        <f t="shared" si="1"/>
+        <v>26.2</v>
+      </c>
+      <c r="N56" s="138">
+        <f t="shared" si="2"/>
+        <v>23.638222222222222</v>
+      </c>
+      <c r="O56" s="139">
+        <v>5</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="S56" s="3">
+        <v>3.0832999999999999</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B57" s="94">
+        <v>112.5</v>
+      </c>
+      <c r="C57" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D57" s="96">
+        <v>16.2</v>
+      </c>
+      <c r="E57" s="99">
+        <v>6</v>
+      </c>
+      <c r="F57" s="97">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="G57" s="95">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="H57" s="96">
+        <v>0.05</v>
+      </c>
+      <c r="I57" s="114">
+        <v>0.193</v>
+      </c>
+      <c r="J57" s="97" t="s">
+        <v>181</v>
+      </c>
+      <c r="L57" s="138">
+        <f t="shared" si="0"/>
+        <v>131</v>
+      </c>
+      <c r="M57" s="138">
+        <f t="shared" si="1"/>
+        <v>26.2</v>
+      </c>
+      <c r="N57" s="138">
+        <f t="shared" si="2"/>
+        <v>18.863999999999997</v>
+      </c>
+      <c r="O57" s="139">
+        <v>6</v>
+      </c>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3">
+        <v>3.0855000000000001</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="58" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B58" s="94">
+        <v>162</v>
+      </c>
+      <c r="C58" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D58" s="96">
+        <v>11.3</v>
+      </c>
+      <c r="E58" s="99">
+        <v>7</v>
+      </c>
+      <c r="F58" s="97">
+        <v>0.22875000000000001</v>
+      </c>
+      <c r="G58" s="95">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="H58" s="96">
+        <v>0.4</v>
+      </c>
+      <c r="I58" s="114">
+        <v>0.35</v>
+      </c>
+      <c r="J58" s="97" t="s">
+        <v>182</v>
+      </c>
+      <c r="L58" s="138">
+        <f t="shared" si="0"/>
+        <v>188.64</v>
+      </c>
+      <c r="M58" s="138">
+        <f t="shared" si="1"/>
+        <v>26.2</v>
+      </c>
+      <c r="N58" s="138">
+        <f t="shared" si="2"/>
+        <v>13.158222222222223</v>
+      </c>
+      <c r="O58" s="139">
+        <v>7</v>
+      </c>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3">
+        <v>3.0832999999999999</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="59" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B59" s="94">
+        <v>202.5</v>
+      </c>
+      <c r="C59" s="94">
+        <v>22.5</v>
+      </c>
+      <c r="D59" s="96">
+        <v>9</v>
+      </c>
+      <c r="E59" s="99">
+        <v>8</v>
+      </c>
+      <c r="F59" s="97">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G59" s="95">
+        <v>0.374</v>
+      </c>
+      <c r="H59" s="96">
+        <v>1</v>
+      </c>
+      <c r="I59" s="114">
+        <v>0.499</v>
+      </c>
+      <c r="J59" s="97" t="s">
+        <v>183</v>
+      </c>
+      <c r="L59" s="138">
+        <f t="shared" si="0"/>
+        <v>235.79999999999998</v>
+      </c>
+      <c r="M59" s="138">
+        <f t="shared" si="1"/>
+        <v>26.2</v>
+      </c>
+      <c r="N59" s="138">
+        <f t="shared" si="2"/>
+        <v>10.48</v>
+      </c>
+      <c r="O59" s="139">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B60" s="105">
+        <v>90</v>
+      </c>
+      <c r="C60" s="105">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D60" s="106">
+        <v>13.5</v>
+      </c>
+      <c r="E60" s="107">
+        <v>9</v>
+      </c>
+      <c r="F60" s="108">
+        <v>0.45124999999999998</v>
+      </c>
+      <c r="G60" s="109">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="H60" s="106">
+        <v>0.05</v>
+      </c>
+      <c r="I60" s="113">
+        <v>0</v>
+      </c>
+      <c r="J60" s="108" t="s">
+        <v>184</v>
+      </c>
+      <c r="L60" s="138">
+        <f t="shared" si="0"/>
+        <v>104.8</v>
+      </c>
+      <c r="M60" s="138">
+        <f t="shared" si="1"/>
+        <v>39.358222222222217</v>
+      </c>
+      <c r="N60" s="138">
+        <f t="shared" si="2"/>
+        <v>15.719999999999999</v>
+      </c>
+      <c r="O60" s="139">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B61" s="94">
+        <v>112.5</v>
+      </c>
+      <c r="C61" s="94">
+        <v>27</v>
+      </c>
+      <c r="D61" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E61" s="99">
+        <v>10</v>
+      </c>
+      <c r="F61" s="97">
+        <v>0.45</v>
+      </c>
+      <c r="G61" s="95">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="H61" s="96">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I61" s="114">
+        <v>0.12</v>
+      </c>
+      <c r="J61" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="L61" s="138">
+        <f t="shared" si="0"/>
+        <v>131</v>
+      </c>
+      <c r="M61" s="138">
+        <f t="shared" si="1"/>
+        <v>31.439999999999998</v>
+      </c>
+      <c r="N61" s="138">
+        <f t="shared" si="2"/>
+        <v>15.719999999999999</v>
+      </c>
+      <c r="O61" s="139">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B62" s="94">
+        <v>162</v>
+      </c>
+      <c r="C62" s="94">
+        <v>18.8</v>
+      </c>
+      <c r="D62" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E62" s="99">
+        <v>11</v>
+      </c>
+      <c r="F62" s="97">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="G62" s="95">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H62" s="96">
+        <v>0.27</v>
+      </c>
+      <c r="I62" s="114">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="J62" s="97" t="s">
+        <v>186</v>
+      </c>
+      <c r="L62" s="138">
+        <f t="shared" si="0"/>
+        <v>188.64</v>
+      </c>
+      <c r="M62" s="138">
+        <f t="shared" si="1"/>
+        <v>21.891555555555556</v>
+      </c>
+      <c r="N62" s="138">
+        <f t="shared" si="2"/>
+        <v>15.719999999999999</v>
+      </c>
+      <c r="O62" s="139">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="94">
+        <v>202.5</v>
+      </c>
+      <c r="C63" s="94">
+        <v>15</v>
+      </c>
+      <c r="D63" s="96">
+        <v>13.5</v>
+      </c>
+      <c r="E63" s="99">
+        <v>12</v>
+      </c>
+      <c r="F63" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="G63" s="95">
+        <v>0</v>
+      </c>
+      <c r="H63" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="I63" s="116">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J63" s="97" t="s">
+        <v>188</v>
+      </c>
+      <c r="L63" s="138">
+        <f t="shared" si="0"/>
+        <v>235.79999999999998</v>
+      </c>
+      <c r="M63" s="138">
+        <f t="shared" si="1"/>
+        <v>17.466666666666665</v>
+      </c>
+      <c r="N63" s="138">
+        <f t="shared" si="2"/>
+        <v>15.719999999999999</v>
+      </c>
+      <c r="O63" s="139">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="3:6" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C65" s="141" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" s="142" t="s">
+        <v>198</v>
+      </c>
+      <c r="E65" s="141" t="s">
+        <v>199</v>
+      </c>
+      <c r="F65" s="141" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C66" s="141">
+        <v>0</v>
+      </c>
+      <c r="D66" s="141">
+        <v>31</v>
+      </c>
+      <c r="E66" s="141">
+        <v>0.80500000000000005</v>
+      </c>
+      <c r="F66" s="144">
+        <v>0.8044</v>
+      </c>
+    </row>
+    <row r="67" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C67" s="141">
+        <v>1</v>
+      </c>
+      <c r="D67" s="141">
+        <v>53.5</v>
+      </c>
+      <c r="E67" s="141">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="F67" s="144">
+        <v>0.32140000000000002</v>
+      </c>
+    </row>
+    <row r="68" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C68" s="141">
+        <v>2</v>
+      </c>
+      <c r="D68" s="141">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E68" s="141">
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="F68" s="144">
+        <v>0.69350000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C69" s="141">
+        <v>3</v>
+      </c>
+      <c r="D69" s="141">
+        <v>22.6</v>
+      </c>
+      <c r="E69" s="141">
+        <v>0.79400000000000004</v>
+      </c>
+      <c r="F69" s="144">
+        <v>0.79330000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C70" s="141">
+        <v>4</v>
+      </c>
+      <c r="D70" s="141">
+        <v>14.9</v>
+      </c>
+      <c r="E70" s="143">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="F70" s="144">
+        <v>0.69940000000000002</v>
+      </c>
+    </row>
+    <row r="71" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C71" s="141">
+        <v>5</v>
+      </c>
+      <c r="D71" s="141">
+        <v>42</v>
+      </c>
+      <c r="E71" s="143">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="F71" s="144">
+        <v>0.82110000000000005</v>
+      </c>
+    </row>
+    <row r="72" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="141">
+        <v>6</v>
+      </c>
+      <c r="D72" s="141">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="E72" s="143">
+        <v>0.84</v>
+      </c>
+      <c r="F72" s="144">
+        <v>0.84109999999999996</v>
+      </c>
+    </row>
+    <row r="73" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C73" s="141">
+        <v>7</v>
+      </c>
+      <c r="D73" s="141">
+        <v>26.6</v>
+      </c>
+      <c r="E73" s="143">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="F73" s="144">
+        <v>0.73960000000000004</v>
+      </c>
+    </row>
+    <row r="74" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C74" s="141">
+        <v>8</v>
+      </c>
+      <c r="D74" s="141">
+        <v>21.8</v>
+      </c>
+      <c r="E74" s="143">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="F74" s="144">
+        <v>0.64270000000000005</v>
+      </c>
+    </row>
+    <row r="75" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C75" s="141">
+        <v>9</v>
+      </c>
+      <c r="D75" s="141">
+        <v>21.8</v>
+      </c>
+      <c r="E75" s="143">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="F75" s="144">
+        <v>0.96419999999999995</v>
+      </c>
+    </row>
+    <row r="76" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="141">
+        <v>10</v>
+      </c>
+      <c r="D76" s="141">
+        <v>26.6</v>
+      </c>
+      <c r="E76" s="143">
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="F76" s="144">
+        <v>0.88749999999999996</v>
+      </c>
+    </row>
+    <row r="77" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="141">
+        <v>11</v>
+      </c>
+      <c r="D77" s="141">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="E77" s="143">
+        <v>0.70099999999999996</v>
+      </c>
+      <c r="F77" s="144">
+        <v>0.70130000000000003</v>
+      </c>
+    </row>
+    <row r="78" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C78" s="141">
+        <v>12</v>
+      </c>
+      <c r="D78" s="141">
+        <v>42</v>
+      </c>
+      <c r="E78" s="143">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="F78" s="144">
+        <v>0.5474</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B51:J63">
+    <sortCondition ref="E51:E63"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
+++ b/hull-form/calcs/Block-Coeff_Ark_royal_calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Ark-Detailed-Design\hull-form\calcs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD030B5-DA7F-40CD-A300-6DF14AAFCF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3ED2D9-6B55-40CC-9FC7-0CD7C2EAEC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="615" windowWidth="21600" windowHeight="14715" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="435" yWindow="945" windowWidth="26085" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="213">
   <si>
     <t>m</t>
   </si>
@@ -388,9 +388,6 @@
     <t>FULL</t>
   </si>
   <si>
-    <t>HONG</t>
-  </si>
-  <si>
     <t>Deadrise</t>
   </si>
   <si>
@@ -635,30 +632,6 @@
   </si>
   <si>
     <t>Ship No.</t>
-  </si>
-  <si>
-    <r>
-      <t>f</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>lim</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t> (degree)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -733,6 +706,42 @@
   <si>
     <t>Cb 0.87</t>
   </si>
+  <si>
+    <t>HIGH Cb</t>
+  </si>
+  <si>
+    <t>CUBIT</t>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>lim</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (deg)</t>
+    </r>
+  </si>
+  <si>
+    <t>Analytical</t>
+  </si>
+  <si>
+    <t>Numerical</t>
+  </si>
 </sst>
 </file>
 
@@ -742,7 +751,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="33" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,8 +976,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1029,8 +1044,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1366,12 +1387,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1495,14 +1527,6 @@
     <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1644,10 +1668,10 @@
     <xf numFmtId="0" fontId="26" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1665,6 +1689,19 @@
     <xf numFmtId="0" fontId="32" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4739,19 +4776,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="26" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>81</v>
       </c>
@@ -4769,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -4788,7 +4826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -4807,7 +4845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -4825,7 +4863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -4843,7 +4881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>86</v>
       </c>
@@ -4851,7 +4889,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -4860,9 +4898,20 @@
         <v>30.342000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="L10" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="N10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="L11" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M11" s="3">
         <f>H18*I18*J18/2</f>
@@ -4872,7 +4921,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B12" s="75"/>
       <c r="C12" s="75"/>
       <c r="D12" s="75"/>
@@ -4883,7 +4932,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>96</v>
       </c>
@@ -4903,10 +4952,10 @@
         <v>47</v>
       </c>
       <c r="L13" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>92</v>
       </c>
@@ -4940,25 +4989,52 @@
         <v>12</v>
       </c>
       <c r="L14" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M14" s="78" t="s">
         <v>116</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="145">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="145">
         <v>0</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="145">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="145">
         <v>3</v>
       </c>
-      <c r="Q14" s="78" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14" s="145">
+        <v>3</v>
+      </c>
+      <c r="S14" s="145">
+        <v>3</v>
+      </c>
+      <c r="T14" s="145">
+        <v>2</v>
+      </c>
+      <c r="U14" s="145">
+        <v>3</v>
+      </c>
+      <c r="V14" s="145">
+        <v>3</v>
+      </c>
+      <c r="W14" s="145">
+        <v>3</v>
+      </c>
+      <c r="X14" s="145">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="145">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="145">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>89</v>
       </c>
@@ -4989,25 +5065,60 @@
         <v>91</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="M15" s="3">
+        <v>118</v>
+      </c>
+      <c r="M15" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="N15" s="147">
         <v>3</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="147">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="147">
         <v>0</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="147">
         <v>2</v>
       </c>
-      <c r="Q15" s="78" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15" s="147">
+        <v>5</v>
+      </c>
+      <c r="S15" s="3">
+        <f>S22*$M$10</f>
+        <v>5.24</v>
+      </c>
+      <c r="T15" s="3">
+        <f>T22*$M$10</f>
+        <v>2.62</v>
+      </c>
+      <c r="U15" s="3">
+        <f>U22*$M$10</f>
+        <v>1.5720000000000001</v>
+      </c>
+      <c r="V15" s="3">
+        <f>V22*$M$10</f>
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="W15" s="3">
+        <f>W22*$M$10</f>
+        <v>2.62</v>
+      </c>
+      <c r="X15" s="3">
+        <f>X22*$M$10</f>
+        <v>3.6680000000000001</v>
+      </c>
+      <c r="Y15" s="3">
+        <f>Y22*$M$10</f>
+        <v>4.1920000000000002</v>
+      </c>
+      <c r="Z15" s="3">
+        <f>Z22*$M$10</f>
+        <v>4.7160000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>90</v>
       </c>
@@ -5040,25 +5151,60 @@
         <v>30</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="M16" s="3">
+        <v>117</v>
+      </c>
+      <c r="M16" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="N16" s="147">
         <v>3</v>
       </c>
-      <c r="N16" s="3">
+      <c r="O16" s="147">
         <v>3</v>
       </c>
-      <c r="O16" s="3">
+      <c r="P16" s="147">
         <v>0</v>
       </c>
-      <c r="P16" s="3">
+      <c r="Q16" s="147">
         <v>2</v>
       </c>
-      <c r="Q16" s="78" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R16" s="147">
+        <v>5</v>
+      </c>
+      <c r="S16" s="3">
+        <f>S23*$M$10</f>
+        <v>5.24</v>
+      </c>
+      <c r="T16" s="3">
+        <f>T23*$M$10</f>
+        <v>2.62</v>
+      </c>
+      <c r="U16" s="3">
+        <f>U23*$M$10</f>
+        <v>1.5720000000000001</v>
+      </c>
+      <c r="V16" s="3">
+        <f>V23*$M$10</f>
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="W16" s="3">
+        <f>W23*$M$10</f>
+        <v>2.62</v>
+      </c>
+      <c r="X16" s="3">
+        <f>X23*$M$10</f>
+        <v>3.6680000000000001</v>
+      </c>
+      <c r="Y16" s="3">
+        <f>Y23*$M$10</f>
+        <v>4.1920000000000002</v>
+      </c>
+      <c r="Z16" s="3">
+        <f>Z23*$M$10</f>
+        <v>4.7160000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>91</v>
       </c>
@@ -5097,23 +5243,50 @@
       <c r="L17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="N17" s="147">
         <v>29381</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="147">
         <v>31624</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="147">
         <v>30012</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="147">
         <v>30507</v>
       </c>
-      <c r="Q17" s="78" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R17" s="147">
+        <v>29479</v>
+      </c>
+      <c r="S17" s="147">
+        <v>29301</v>
+      </c>
+      <c r="T17" s="148">
+        <v>31264</v>
+      </c>
+      <c r="U17" s="148">
+        <v>30771</v>
+      </c>
+      <c r="V17" s="148">
+        <v>30626</v>
+      </c>
+      <c r="W17" s="148">
+        <v>30441</v>
+      </c>
+      <c r="X17" s="148">
+        <v>29952</v>
+      </c>
+      <c r="Y17" s="148">
+        <v>29651</v>
+      </c>
+      <c r="Z17" s="148">
+        <v>29310</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>94</v>
       </c>
@@ -5153,26 +5326,62 @@
         <v>15.72</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="M18" s="5">
-        <f>M17/$M$11</f>
+        <v>120</v>
+      </c>
+      <c r="N18" s="146">
+        <f>N17/$M$11</f>
         <v>0.90759102822004201</v>
       </c>
-      <c r="N18" s="5">
-        <f>N17/$M$11</f>
+      <c r="O18" s="146">
+        <f>O17/$M$11</f>
         <v>0.97687820960588845</v>
       </c>
-      <c r="O18" s="5">
-        <f>O17/$M$11</f>
+      <c r="P18" s="146">
+        <f>P17/$M$11</f>
         <v>0.92708287461079952</v>
       </c>
-      <c r="P18" s="5">
-        <f>P17/$M$11</f>
+      <c r="Q18" s="146">
+        <f>Q17/$M$11</f>
         <v>0.94237362574142547</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R18" s="146">
+        <f>R17/$M$11</f>
+        <v>0.91061828803984268</v>
+      </c>
+      <c r="S18" s="146">
+        <f>S17/$M$11</f>
+        <v>0.9051197957140823</v>
+      </c>
+      <c r="T18" s="146">
+        <f>T17/$M$11</f>
+        <v>0.96575766332906965</v>
+      </c>
+      <c r="U18" s="149">
+        <f>U17/$M$11</f>
+        <v>0.95052869301109266</v>
+      </c>
+      <c r="V18" s="149">
+        <f>V17/$M$11</f>
+        <v>0.94604958409404061</v>
+      </c>
+      <c r="W18" s="149">
+        <f>W17/$M$11</f>
+        <v>0.9403348589240087</v>
+      </c>
+      <c r="X18" s="149">
+        <f>X17/$M$11</f>
+        <v>0.92522945023132974</v>
+      </c>
+      <c r="Y18" s="149">
+        <f>Y17/$M$11</f>
+        <v>0.91593143792765619</v>
+      </c>
+      <c r="Z18" s="149">
+        <f>Z17/$M$11</f>
+        <v>0.90539780937100278</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>95</v>
       </c>
@@ -5197,26 +5406,62 @@
         <v>0.87166807314397887</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="M19" s="68">
-        <f>1-M18</f>
-        <v>9.2408971779957993E-2</v>
+        <v>121</v>
       </c>
       <c r="N19" s="68">
         <f>1-N18</f>
-        <v>2.3121790394111552E-2</v>
+        <v>9.2408971779957993E-2</v>
       </c>
       <c r="O19" s="68">
         <f>1-O18</f>
-        <v>7.2917125389200477E-2</v>
+        <v>2.3121790394111552E-2</v>
       </c>
       <c r="P19" s="68">
         <f>1-P18</f>
+        <v>7.2917125389200477E-2</v>
+      </c>
+      <c r="Q19" s="68">
+        <f>1-Q18</f>
         <v>5.7626374258574531E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R19" s="68">
+        <f>1-R18</f>
+        <v>8.9381711960157317E-2</v>
+      </c>
+      <c r="S19" s="68">
+        <f>1-S18</f>
+        <v>9.4880204285917702E-2</v>
+      </c>
+      <c r="T19" s="68">
+        <f>1-T18</f>
+        <v>3.4242336670930351E-2</v>
+      </c>
+      <c r="U19" s="68">
+        <f>1-U18</f>
+        <v>4.9471306988907338E-2</v>
+      </c>
+      <c r="V19" s="68">
+        <f>1-V18</f>
+        <v>5.3950415905959392E-2</v>
+      </c>
+      <c r="W19" s="68">
+        <f>1-W18</f>
+        <v>5.9665141075991301E-2</v>
+      </c>
+      <c r="X19" s="68">
+        <f>1-X18</f>
+        <v>7.4770549768670258E-2</v>
+      </c>
+      <c r="Y19" s="68">
+        <f>1-Y18</f>
+        <v>8.4068562072343811E-2</v>
+      </c>
+      <c r="Z19" s="68">
+        <f>1-Z18</f>
+        <v>9.4602190628997218E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
@@ -5241,31 +5486,81 @@
         <v>107</v>
       </c>
       <c r="I20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J20">
         <f>H18*I18*J18</f>
         <v>64745.020799999991</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J21">
         <v>1.0249999999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J22">
         <f>J20*J21/2</f>
         <v>33181.823159999993</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="N22" s="3">
+        <f>N15/$M$10</f>
+        <v>5.7251908396946565</v>
+      </c>
+      <c r="O22" s="3">
+        <f t="shared" ref="O22:R22" si="3">O15/$M$10</f>
+        <v>5.7251908396946565</v>
+      </c>
+      <c r="P22" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <f t="shared" si="3"/>
+        <v>3.8167938931297707</v>
+      </c>
+      <c r="R22" s="3">
+        <f t="shared" si="3"/>
+        <v>9.5419847328244263</v>
+      </c>
+      <c r="S22" s="147">
+        <v>10</v>
+      </c>
+      <c r="T22" s="147">
+        <v>5</v>
+      </c>
+      <c r="U22" s="147">
+        <v>3</v>
+      </c>
+      <c r="V22" s="147">
+        <v>4</v>
+      </c>
+      <c r="W22" s="147">
+        <v>5</v>
+      </c>
+      <c r="X22" s="147">
+        <v>7</v>
+      </c>
+      <c r="Y22" s="147">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="147">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>106</v>
       </c>
@@ -5277,14 +5572,61 @@
         <v>88</v>
       </c>
       <c r="I23" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J23">
         <f>J22*0.87</f>
         <v>28868.186149199992</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="N23" s="3">
+        <f>N16/$M$10</f>
+        <v>5.7251908396946565</v>
+      </c>
+      <c r="O23" s="3">
+        <f t="shared" ref="O23:R23" si="4">O16/$M$10</f>
+        <v>5.7251908396946565</v>
+      </c>
+      <c r="P23" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" si="4"/>
+        <v>3.8167938931297707</v>
+      </c>
+      <c r="R23" s="3">
+        <f t="shared" si="4"/>
+        <v>9.5419847328244263</v>
+      </c>
+      <c r="S23" s="147">
+        <v>10</v>
+      </c>
+      <c r="T23" s="147">
+        <v>5</v>
+      </c>
+      <c r="U23" s="147">
+        <v>3</v>
+      </c>
+      <c r="V23" s="147">
+        <v>4</v>
+      </c>
+      <c r="W23" s="147">
+        <v>5</v>
+      </c>
+      <c r="X23" s="147">
+        <v>7</v>
+      </c>
+      <c r="Y23" s="147">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="147">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>102</v>
       </c>
@@ -5294,11 +5636,8 @@
       <c r="C24" t="s">
         <v>103</v>
       </c>
-      <c r="R24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>104</v>
       </c>
@@ -5310,7 +5649,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>109</v>
       </c>
@@ -5322,7 +5661,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>112</v>
       </c>
@@ -5334,7 +5673,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>111</v>
       </c>
@@ -5361,82 +5700,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="141" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="87"/>
-    </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="88"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="89" t="s">
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="90" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="80" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="81" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="81" t="s">
+      <c r="D8" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="E8" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="F8" s="81" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="H8" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="I8" s="81" t="s">
         <v>130</v>
-      </c>
-      <c r="E8" s="81" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="81" t="s">
-        <v>163</v>
-      </c>
-      <c r="G8" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="H8" s="81" t="s">
-        <v>166</v>
-      </c>
-      <c r="I8" s="81" t="s">
-        <v>131</v>
       </c>
       <c r="K8">
         <v>9</v>
@@ -5450,7 +5789,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="83">
         <v>157.19999999999999</v>
@@ -5471,7 +5810,7 @@
         <v>90</v>
       </c>
       <c r="I9" s="79" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K9">
         <f>F9/E9</f>
@@ -5488,7 +5827,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" s="83">
         <v>26.2</v>
@@ -5509,7 +5848,7 @@
         <v>22.5</v>
       </c>
       <c r="I10" s="79" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K10">
         <f>F10/E10</f>
@@ -5526,7 +5865,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="82" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" s="83">
         <v>0.87</v>
@@ -5547,7 +5886,7 @@
         <v>0.94</v>
       </c>
       <c r="I11" s="79" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K11">
         <f>F11/E11</f>
@@ -5564,7 +5903,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="82" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="83">
         <v>7.86</v>
@@ -5589,7 +5928,7 @@
         <v>10.15</v>
       </c>
       <c r="I12" s="79" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K12">
         <f>F12/E12</f>
@@ -5606,7 +5945,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="82" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C13" s="84">
         <f>10.75-((300-C9)/100)^1.5</f>
@@ -5633,41 +5972,41 @@
         <v>7.7068108833002178</v>
       </c>
       <c r="I13" s="79" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B16" s="81"/>
       <c r="C16" s="81" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="81" t="s">
+      <c r="E16" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="81" t="s">
+        <v>162</v>
+      </c>
+      <c r="G16" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="I16" s="81" t="s">
         <v>130</v>
-      </c>
-      <c r="E16" s="81" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="81" t="s">
-        <v>163</v>
-      </c>
-      <c r="G16" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="H16" s="81" t="s">
-        <v>166</v>
-      </c>
-      <c r="I16" s="81" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="82" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="85">
         <f>110*C13*C9^2*C10*(C11+0.7)*0.001</f>
@@ -5694,7 +6033,7 @@
         <v>253383.75754005619</v>
       </c>
       <c r="I17" s="79" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K17">
         <f>F17/E17</f>
@@ -5711,7 +6050,7 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B18" s="82" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="85">
         <f>190*C13*C9^2*C10*(C11+0.7)*0.001</f>
@@ -5738,7 +6077,7 @@
         <v>437662.85393282439</v>
       </c>
       <c r="I18" s="79" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K18">
         <f>F18/E18</f>
@@ -5755,7 +6094,7 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B19" s="82" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C19" s="85">
         <f>C17/1000</f>
@@ -5797,7 +6136,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B20" s="82" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C20" s="85">
         <f>C18/1000</f>
@@ -5838,16 +6177,16 @@
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="90" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="90"/>
+      <c r="B22" s="144" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="144"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="144"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="144"/>
       <c r="K22">
         <f t="shared" ref="K22:L22" si="11">1/K20</f>
         <v>1.6773026526149832</v>
@@ -5863,7 +6202,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
@@ -5874,7 +6213,7 @@
         <v>17.5</v>
       </c>
       <c r="D25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E25">
         <f>E9/$C$27</f>
@@ -5902,7 +6241,7 @@
         <v>12</v>
       </c>
       <c r="E26">
-        <f t="shared" ref="E26:G27" si="13">E10/$C$27</f>
+        <f t="shared" ref="E26" si="13">E10/$C$27</f>
         <v>50</v>
       </c>
       <c r="F26">
@@ -5956,1248 +6295,1251 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F61EFB5-6D33-40B3-B388-0C63A65D83F2}">
-  <dimension ref="B2:T78"/>
+  <dimension ref="B2:T76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="32.5703125" customWidth="1"/>
     <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.28515625" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="91" t="s">
+      <c r="D2" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="98" t="s">
-        <v>189</v>
-      </c>
-      <c r="F2" s="91" t="s">
+      <c r="E2" s="94" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2" s="87" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="G2" s="92" t="s">
+      <c r="H2" s="89" t="s">
         <v>170</v>
       </c>
-      <c r="H2" s="93" t="s">
+      <c r="I2" s="89" t="s">
         <v>171</v>
       </c>
-      <c r="I2" s="93" t="s">
+      <c r="J2" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="J2" s="93" t="s">
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="125">
+        <v>135</v>
+      </c>
+      <c r="C3" s="125">
+        <v>22.5</v>
+      </c>
+      <c r="D3" s="126">
+        <v>13.5</v>
+      </c>
+      <c r="E3" s="127">
+        <v>0</v>
+      </c>
+      <c r="F3" s="128" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="129">
+      <c r="G3" s="129">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H3" s="125">
+        <v>0.15</v>
+      </c>
+      <c r="I3" s="125">
+        <v>0.247</v>
+      </c>
+      <c r="J3" s="125" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="90">
         <v>135</v>
       </c>
-      <c r="C3" s="129">
+      <c r="C4" s="90">
+        <v>15</v>
+      </c>
+      <c r="D4" s="92">
+        <v>20.3</v>
+      </c>
+      <c r="E4" s="95">
+        <v>1</v>
+      </c>
+      <c r="F4" s="93">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="G4" s="91">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="H4" s="90">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="90">
+        <v>1</v>
+      </c>
+      <c r="J4" s="90" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="90">
+        <v>135</v>
+      </c>
+      <c r="C5" s="90">
+        <v>18.8</v>
+      </c>
+      <c r="D5" s="92">
+        <v>16.2</v>
+      </c>
+      <c r="E5" s="95">
+        <v>2</v>
+      </c>
+      <c r="F5" s="93">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="G5" s="91">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="H5" s="90">
+        <v>0.11</v>
+      </c>
+      <c r="I5" s="90">
+        <v>0.42</v>
+      </c>
+      <c r="J5" s="90" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="90">
+        <v>135</v>
+      </c>
+      <c r="C6" s="90">
+        <v>27</v>
+      </c>
+      <c r="D6" s="92">
+        <v>11.25</v>
+      </c>
+      <c r="E6" s="95">
+        <v>3</v>
+      </c>
+      <c r="F6" s="93">
+        <v>0.31125000000000003</v>
+      </c>
+      <c r="G6" s="91">
+        <v>0.308</v>
+      </c>
+      <c r="H6" s="90">
+        <v>0.2</v>
+      </c>
+      <c r="I6" s="90">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J6" s="90" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="90">
+        <v>135</v>
+      </c>
+      <c r="C7" s="90">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D7" s="92">
+        <v>9</v>
+      </c>
+      <c r="E7" s="95">
+        <v>4</v>
+      </c>
+      <c r="F7" s="93">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="G7" s="91">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H7" s="90">
+        <v>0.35</v>
+      </c>
+      <c r="I7" s="90">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="J7" s="90" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="96">
+        <v>90</v>
+      </c>
+      <c r="C8" s="96">
         <v>22.5</v>
       </c>
-      <c r="D3" s="130">
+      <c r="D8" s="97">
+        <v>20.3</v>
+      </c>
+      <c r="E8" s="98">
+        <v>5</v>
+      </c>
+      <c r="F8" s="99">
+        <v>0.66</v>
+      </c>
+      <c r="G8" s="100">
+        <v>1</v>
+      </c>
+      <c r="H8" s="96">
+        <v>0</v>
+      </c>
+      <c r="I8" s="96">
+        <v>0.222</v>
+      </c>
+      <c r="J8" s="96" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="90">
+        <v>112.5</v>
+      </c>
+      <c r="C9" s="90">
+        <v>22.5</v>
+      </c>
+      <c r="D9" s="92">
+        <v>16.2</v>
+      </c>
+      <c r="E9" s="95">
+        <v>6</v>
+      </c>
+      <c r="F9" s="93">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="G9" s="91">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="H9" s="90">
+        <v>0.05</v>
+      </c>
+      <c r="I9" s="90">
+        <v>0.193</v>
+      </c>
+      <c r="J9" s="90" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="90">
+        <v>162</v>
+      </c>
+      <c r="C10" s="90">
+        <v>22.5</v>
+      </c>
+      <c r="D10" s="92">
+        <v>11.3</v>
+      </c>
+      <c r="E10" s="95">
+        <v>7</v>
+      </c>
+      <c r="F10" s="93">
+        <v>0.22875000000000001</v>
+      </c>
+      <c r="G10" s="91">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="H10" s="90">
+        <v>0.4</v>
+      </c>
+      <c r="I10" s="90">
+        <v>0.35</v>
+      </c>
+      <c r="J10" s="90" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="90">
+        <v>202.5</v>
+      </c>
+      <c r="C11" s="90">
+        <v>22.5</v>
+      </c>
+      <c r="D11" s="92">
+        <v>9</v>
+      </c>
+      <c r="E11" s="95">
+        <v>8</v>
+      </c>
+      <c r="F11" s="93">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G11" s="91">
+        <v>0.374</v>
+      </c>
+      <c r="H11" s="90">
+        <v>1</v>
+      </c>
+      <c r="I11" s="90">
+        <v>0.499</v>
+      </c>
+      <c r="J11" s="90" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="101">
+        <v>90</v>
+      </c>
+      <c r="C12" s="101">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D12" s="102">
         <v>13.5</v>
       </c>
-      <c r="E3" s="131">
+      <c r="E12" s="103">
+        <v>9</v>
+      </c>
+      <c r="F12" s="104">
+        <v>0.45124999999999998</v>
+      </c>
+      <c r="G12" s="105">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="H12" s="101">
+        <v>0.05</v>
+      </c>
+      <c r="I12" s="101">
         <v>0</v>
       </c>
-      <c r="F3" s="132" t="s">
-        <v>174</v>
-      </c>
-      <c r="G3" s="133">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="H3" s="129">
-        <v>0.15</v>
-      </c>
-      <c r="I3" s="129">
-        <v>0.247</v>
-      </c>
-      <c r="J3" s="129" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="94">
-        <v>135</v>
-      </c>
-      <c r="C4" s="94">
+      <c r="J12" s="101" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="90">
+        <v>112.5</v>
+      </c>
+      <c r="C13" s="90">
+        <v>27</v>
+      </c>
+      <c r="D13" s="92">
+        <v>13.5</v>
+      </c>
+      <c r="E13" s="95">
+        <v>10</v>
+      </c>
+      <c r="F13" s="93">
+        <v>0.45</v>
+      </c>
+      <c r="G13" s="91">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="H13" s="90">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I13" s="90">
+        <v>0.12</v>
+      </c>
+      <c r="J13" s="90" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="90">
+        <v>162</v>
+      </c>
+      <c r="C14" s="90">
+        <v>18.8</v>
+      </c>
+      <c r="D14" s="92">
+        <v>13.5</v>
+      </c>
+      <c r="E14" s="95">
+        <v>11</v>
+      </c>
+      <c r="F14" s="93">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="G14" s="91">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H14" s="90">
+        <v>0.27</v>
+      </c>
+      <c r="I14" s="90">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="J14" s="90" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="90">
+        <v>202.5</v>
+      </c>
+      <c r="C15" s="90">
         <v>15</v>
       </c>
-      <c r="D4" s="96">
-        <v>20.3</v>
-      </c>
-      <c r="E4" s="99">
-        <v>1</v>
-      </c>
-      <c r="F4" s="97">
-        <v>0.41249999999999998</v>
-      </c>
-      <c r="G4" s="95">
-        <v>0.50700000000000001</v>
-      </c>
-      <c r="H4" s="94">
-        <v>0.1</v>
-      </c>
-      <c r="I4" s="94">
-        <v>1</v>
-      </c>
-      <c r="J4" s="94" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="94">
-        <v>135</v>
-      </c>
-      <c r="C5" s="94">
-        <v>18.8</v>
-      </c>
-      <c r="D5" s="96">
-        <v>16.2</v>
-      </c>
-      <c r="E5" s="99">
-        <v>2</v>
-      </c>
-      <c r="F5" s="97">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="G5" s="95">
-        <v>0.61099999999999999</v>
-      </c>
-      <c r="H5" s="94">
-        <v>0.11</v>
-      </c>
-      <c r="I5" s="94">
-        <v>0.42</v>
-      </c>
-      <c r="J5" s="94" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="94">
-        <v>135</v>
-      </c>
-      <c r="C6" s="94">
-        <v>27</v>
-      </c>
-      <c r="D6" s="96">
-        <v>11.25</v>
-      </c>
-      <c r="E6" s="99">
-        <v>3</v>
-      </c>
-      <c r="F6" s="97">
-        <v>0.31125000000000003</v>
-      </c>
-      <c r="G6" s="95">
-        <v>0.308</v>
-      </c>
-      <c r="H6" s="94">
-        <v>0.2</v>
-      </c>
-      <c r="I6" s="94">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="J6" s="94" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="94">
-        <v>135</v>
-      </c>
-      <c r="C7" s="94">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="D7" s="96">
-        <v>9</v>
-      </c>
-      <c r="E7" s="99">
-        <v>4</v>
-      </c>
-      <c r="F7" s="97">
-        <v>0.24374999999999999</v>
-      </c>
-      <c r="G7" s="95">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="H7" s="94">
-        <v>0.35</v>
-      </c>
-      <c r="I7" s="94">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="J7" s="94" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="100">
-        <v>90</v>
-      </c>
-      <c r="C8" s="100">
-        <v>22.5</v>
-      </c>
-      <c r="D8" s="101">
-        <v>20.3</v>
-      </c>
-      <c r="E8" s="102">
-        <v>5</v>
-      </c>
-      <c r="F8" s="103">
-        <v>0.66</v>
-      </c>
-      <c r="G8" s="104">
-        <v>1</v>
-      </c>
-      <c r="H8" s="100">
+      <c r="D15" s="92">
+        <v>13.5</v>
+      </c>
+      <c r="E15" s="95">
+        <v>12</v>
+      </c>
+      <c r="F15" s="93" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" s="91">
         <v>0</v>
       </c>
-      <c r="I8" s="100">
-        <v>0.222</v>
-      </c>
-      <c r="J8" s="100" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="94">
-        <v>112.5</v>
-      </c>
-      <c r="C9" s="94">
-        <v>22.5</v>
-      </c>
-      <c r="D9" s="96">
-        <v>16.2</v>
-      </c>
-      <c r="E9" s="99">
-        <v>6</v>
-      </c>
-      <c r="F9" s="97">
-        <v>0.54749999999999999</v>
-      </c>
-      <c r="G9" s="95">
-        <v>0.77300000000000002</v>
-      </c>
-      <c r="H9" s="94">
-        <v>0.05</v>
-      </c>
-      <c r="I9" s="94">
-        <v>0.193</v>
-      </c>
-      <c r="J9" s="94" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="94">
-        <v>162</v>
-      </c>
-      <c r="C10" s="94">
-        <v>22.5</v>
-      </c>
-      <c r="D10" s="96">
-        <v>11.3</v>
-      </c>
-      <c r="E10" s="99">
-        <v>7</v>
-      </c>
-      <c r="F10" s="97">
-        <v>0.22875000000000001</v>
-      </c>
-      <c r="G10" s="95">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="H10" s="94">
-        <v>0.4</v>
-      </c>
-      <c r="I10" s="94">
-        <v>0.35</v>
-      </c>
-      <c r="J10" s="94" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="94">
-        <v>202.5</v>
-      </c>
-      <c r="C11" s="94">
-        <v>22.5</v>
-      </c>
-      <c r="D11" s="96">
-        <v>9</v>
-      </c>
-      <c r="E11" s="99">
-        <v>8</v>
-      </c>
-      <c r="F11" s="97">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="G11" s="95">
-        <v>0.374</v>
-      </c>
-      <c r="H11" s="94">
-        <v>1</v>
-      </c>
-      <c r="I11" s="94">
-        <v>0.499</v>
-      </c>
-      <c r="J11" s="94" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="105">
-        <v>90</v>
-      </c>
-      <c r="C12" s="105">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="D12" s="106">
-        <v>13.5</v>
-      </c>
-      <c r="E12" s="107">
-        <v>9</v>
-      </c>
-      <c r="F12" s="108">
-        <v>0.45124999999999998</v>
-      </c>
-      <c r="G12" s="109">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="H12" s="105">
-        <v>0.05</v>
-      </c>
-      <c r="I12" s="105">
-        <v>0</v>
-      </c>
-      <c r="J12" s="105" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="94">
-        <v>112.5</v>
-      </c>
-      <c r="C13" s="94">
-        <v>27</v>
-      </c>
-      <c r="D13" s="96">
-        <v>13.5</v>
-      </c>
-      <c r="E13" s="99">
-        <v>10</v>
-      </c>
-      <c r="F13" s="97">
-        <v>0.45</v>
-      </c>
-      <c r="G13" s="95">
-        <v>0.58099999999999996</v>
-      </c>
-      <c r="H13" s="94">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="I13" s="94">
-        <v>0.12</v>
-      </c>
-      <c r="J13" s="94" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="94">
-        <v>162</v>
-      </c>
-      <c r="C14" s="94">
-        <v>18.8</v>
-      </c>
-      <c r="D14" s="96">
-        <v>13.5</v>
-      </c>
-      <c r="E14" s="99">
-        <v>11</v>
-      </c>
-      <c r="F14" s="97">
-        <v>0.30249999999999999</v>
-      </c>
-      <c r="G14" s="95">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="H14" s="94">
-        <v>0.27</v>
-      </c>
-      <c r="I14" s="94">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="J14" s="94" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B15" s="94">
-        <v>202.5</v>
-      </c>
-      <c r="C15" s="94">
-        <v>15</v>
-      </c>
-      <c r="D15" s="96">
-        <v>13.5</v>
-      </c>
-      <c r="E15" s="99">
-        <v>12</v>
-      </c>
-      <c r="F15" s="97" t="s">
+      <c r="H15" s="90">
+        <v>0.65</v>
+      </c>
+      <c r="I15" s="90">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J15" s="90" t="s">
         <v>187</v>
-      </c>
-      <c r="G15" s="95">
-        <v>0</v>
-      </c>
-      <c r="H15" s="94">
-        <v>0.65</v>
-      </c>
-      <c r="I15" s="94">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="J15" s="94" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="91" t="s">
+      <c r="B18" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="91" t="s">
+      <c r="C18" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="91" t="s">
+      <c r="D18" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="98" t="s">
-        <v>189</v>
-      </c>
-      <c r="F18" s="121" t="s">
+      <c r="E18" s="94" t="s">
+        <v>188</v>
+      </c>
+      <c r="F18" s="117" t="s">
+        <v>168</v>
+      </c>
+      <c r="G18" s="121" t="s">
         <v>169</v>
       </c>
-      <c r="G18" s="125" t="s">
+      <c r="H18" s="107" t="s">
         <v>170</v>
       </c>
-      <c r="H18" s="111" t="s">
+      <c r="I18" s="89" t="s">
         <v>171</v>
       </c>
-      <c r="I18" s="93" t="s">
+      <c r="J18" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="J18" s="93" t="s">
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="90">
+        <v>202.5</v>
+      </c>
+      <c r="C19" s="90">
+        <v>15</v>
+      </c>
+      <c r="D19" s="92">
+        <v>13.5</v>
+      </c>
+      <c r="E19" s="95">
+        <v>12</v>
+      </c>
+      <c r="F19" s="118" t="s">
+        <v>186</v>
+      </c>
+      <c r="G19" s="122">
+        <v>0</v>
+      </c>
+      <c r="H19" s="93">
+        <v>0.65</v>
+      </c>
+      <c r="I19" s="90">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J19" s="90" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="90">
+        <v>162</v>
+      </c>
+      <c r="C20" s="90">
+        <v>22.5</v>
+      </c>
+      <c r="D20" s="92">
+        <v>11.3</v>
+      </c>
+      <c r="E20" s="95">
+        <v>7</v>
+      </c>
+      <c r="F20" s="118">
+        <v>0.22875000000000001</v>
+      </c>
+      <c r="G20" s="122">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="H20" s="93">
+        <v>0.4</v>
+      </c>
+      <c r="I20" s="90">
+        <v>0.35</v>
+      </c>
+      <c r="J20" s="90" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="90">
+        <v>135</v>
+      </c>
+      <c r="C21" s="90">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D21" s="92">
+        <v>9</v>
+      </c>
+      <c r="E21" s="95">
+        <v>4</v>
+      </c>
+      <c r="F21" s="118">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="G21" s="122">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H21" s="93">
+        <v>0.35</v>
+      </c>
+      <c r="I21" s="90">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="J21" s="90" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="90">
+        <v>162</v>
+      </c>
+      <c r="C22" s="90">
+        <v>18.8</v>
+      </c>
+      <c r="D22" s="92">
+        <v>13.5</v>
+      </c>
+      <c r="E22" s="95">
+        <v>11</v>
+      </c>
+      <c r="F22" s="118">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="G22" s="122">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H22" s="93">
+        <v>0.27</v>
+      </c>
+      <c r="I22" s="90">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="J22" s="90" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="90">
+        <v>135</v>
+      </c>
+      <c r="C23" s="90">
+        <v>27</v>
+      </c>
+      <c r="D23" s="92">
+        <v>11.25</v>
+      </c>
+      <c r="E23" s="95">
+        <v>3</v>
+      </c>
+      <c r="F23" s="118">
+        <v>0.31125000000000003</v>
+      </c>
+      <c r="G23" s="122">
+        <v>0.308</v>
+      </c>
+      <c r="H23" s="93">
+        <v>0.2</v>
+      </c>
+      <c r="I23" s="90">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J23" s="90" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="90">
+        <v>202.5</v>
+      </c>
+      <c r="C24" s="90">
+        <v>22.5</v>
+      </c>
+      <c r="D24" s="92">
+        <v>9</v>
+      </c>
+      <c r="E24" s="95">
+        <v>8</v>
+      </c>
+      <c r="F24" s="118">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G24" s="122">
+        <v>0.374</v>
+      </c>
+      <c r="H24" s="93">
+        <v>1</v>
+      </c>
+      <c r="I24" s="90">
+        <v>0.499</v>
+      </c>
+      <c r="J24" s="90" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="125">
+        <v>135</v>
+      </c>
+      <c r="C25" s="125">
+        <v>22.5</v>
+      </c>
+      <c r="D25" s="126">
+        <v>13.5</v>
+      </c>
+      <c r="E25" s="127">
+        <v>0</v>
+      </c>
+      <c r="F25" s="130" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="94">
-        <v>202.5</v>
-      </c>
-      <c r="C19" s="94">
+      <c r="G25" s="131">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H25" s="128">
+        <v>0.15</v>
+      </c>
+      <c r="I25" s="125">
+        <v>0.247</v>
+      </c>
+      <c r="J25" s="125" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="90">
+        <v>135</v>
+      </c>
+      <c r="C26" s="90">
         <v>15</v>
       </c>
-      <c r="D19" s="96">
+      <c r="D26" s="92">
+        <v>20.3</v>
+      </c>
+      <c r="E26" s="95">
+        <v>1</v>
+      </c>
+      <c r="F26" s="118">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="G26" s="122">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="H26" s="93">
+        <v>0.1</v>
+      </c>
+      <c r="I26" s="90">
+        <v>1</v>
+      </c>
+      <c r="J26" s="90" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="90">
+        <v>112.5</v>
+      </c>
+      <c r="C27" s="90">
+        <v>27</v>
+      </c>
+      <c r="D27" s="92">
         <v>13.5</v>
       </c>
-      <c r="E19" s="99">
-        <v>12</v>
-      </c>
-      <c r="F19" s="122" t="s">
-        <v>187</v>
-      </c>
-      <c r="G19" s="126">
+      <c r="E27" s="95">
+        <v>10</v>
+      </c>
+      <c r="F27" s="118">
+        <v>0.45</v>
+      </c>
+      <c r="G27" s="122">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="H27" s="93">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I27" s="90">
+        <v>0.12</v>
+      </c>
+      <c r="J27" s="90" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="101">
+        <v>90</v>
+      </c>
+      <c r="C28" s="101">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D28" s="102">
+        <v>13.5</v>
+      </c>
+      <c r="E28" s="103">
+        <v>9</v>
+      </c>
+      <c r="F28" s="119">
+        <v>0.45124999999999998</v>
+      </c>
+      <c r="G28" s="123">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="H28" s="104">
+        <v>0.05</v>
+      </c>
+      <c r="I28" s="101">
         <v>0</v>
       </c>
-      <c r="H19" s="97">
-        <v>0.65</v>
-      </c>
-      <c r="I19" s="94">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="J19" s="94" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="94">
-        <v>162</v>
-      </c>
-      <c r="C20" s="94">
+      <c r="J28" s="101" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="90">
+        <v>135</v>
+      </c>
+      <c r="C29" s="90">
+        <v>18.8</v>
+      </c>
+      <c r="D29" s="92">
+        <v>16.2</v>
+      </c>
+      <c r="E29" s="95">
+        <v>2</v>
+      </c>
+      <c r="F29" s="118">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="G29" s="122">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="H29" s="93">
+        <v>0.11</v>
+      </c>
+      <c r="I29" s="90">
+        <v>0.42</v>
+      </c>
+      <c r="J29" s="90" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="90">
+        <v>112.5</v>
+      </c>
+      <c r="C30" s="90">
         <v>22.5</v>
       </c>
-      <c r="D20" s="96">
-        <v>11.3</v>
-      </c>
-      <c r="E20" s="99">
-        <v>7</v>
-      </c>
-      <c r="F20" s="122">
-        <v>0.22875000000000001</v>
-      </c>
-      <c r="G20" s="126">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="H20" s="97">
-        <v>0.4</v>
-      </c>
-      <c r="I20" s="94">
-        <v>0.35</v>
-      </c>
-      <c r="J20" s="94" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="94">
-        <v>135</v>
-      </c>
-      <c r="C21" s="94">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="D21" s="96">
-        <v>9</v>
-      </c>
-      <c r="E21" s="99">
-        <v>4</v>
-      </c>
-      <c r="F21" s="122">
-        <v>0.24374999999999999</v>
-      </c>
-      <c r="G21" s="126">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="H21" s="97">
-        <v>0.35</v>
-      </c>
-      <c r="I21" s="94">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="J21" s="94" t="s">
+      <c r="D30" s="92">
+        <v>16.2</v>
+      </c>
+      <c r="E30" s="95">
+        <v>6</v>
+      </c>
+      <c r="F30" s="118">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="G30" s="122">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="H30" s="93">
+        <v>0.05</v>
+      </c>
+      <c r="I30" s="90">
+        <v>0.193</v>
+      </c>
+      <c r="J30" s="90" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="96">
+        <v>90</v>
+      </c>
+      <c r="C31" s="96">
+        <v>22.5</v>
+      </c>
+      <c r="D31" s="97">
+        <v>20.3</v>
+      </c>
+      <c r="E31" s="98">
+        <v>5</v>
+      </c>
+      <c r="F31" s="120">
+        <v>0.66</v>
+      </c>
+      <c r="G31" s="124">
+        <v>1</v>
+      </c>
+      <c r="H31" s="99">
+        <v>0</v>
+      </c>
+      <c r="I31" s="96">
+        <v>0.222</v>
+      </c>
+      <c r="J31" s="96" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="94">
-        <v>162</v>
-      </c>
-      <c r="C22" s="94">
-        <v>18.8</v>
-      </c>
-      <c r="D22" s="96">
-        <v>13.5</v>
-      </c>
-      <c r="E22" s="99">
-        <v>11</v>
-      </c>
-      <c r="F22" s="122">
-        <v>0.30249999999999999</v>
-      </c>
-      <c r="G22" s="126">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="H22" s="97">
-        <v>0.27</v>
-      </c>
-      <c r="I22" s="94">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="J22" s="94" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="94">
-        <v>135</v>
-      </c>
-      <c r="C23" s="94">
-        <v>27</v>
-      </c>
-      <c r="D23" s="96">
-        <v>11.25</v>
-      </c>
-      <c r="E23" s="99">
-        <v>3</v>
-      </c>
-      <c r="F23" s="122">
-        <v>0.31125000000000003</v>
-      </c>
-      <c r="G23" s="126">
-        <v>0.308</v>
-      </c>
-      <c r="H23" s="97">
-        <v>0.2</v>
-      </c>
-      <c r="I23" s="94">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="J23" s="94" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="94">
-        <v>202.5</v>
-      </c>
-      <c r="C24" s="94">
-        <v>22.5</v>
-      </c>
-      <c r="D24" s="96">
-        <v>9</v>
-      </c>
-      <c r="E24" s="99">
-        <v>8</v>
-      </c>
-      <c r="F24" s="122">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="G24" s="126">
-        <v>0.374</v>
-      </c>
-      <c r="H24" s="97">
-        <v>1</v>
-      </c>
-      <c r="I24" s="94">
-        <v>0.499</v>
-      </c>
-      <c r="J24" s="94" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="129">
-        <v>135</v>
-      </c>
-      <c r="C25" s="129">
-        <v>22.5</v>
-      </c>
-      <c r="D25" s="130">
-        <v>13.5</v>
-      </c>
-      <c r="E25" s="131">
-        <v>0</v>
-      </c>
-      <c r="F25" s="134" t="s">
-        <v>174</v>
-      </c>
-      <c r="G25" s="135">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="H25" s="132">
-        <v>0.15</v>
-      </c>
-      <c r="I25" s="129">
-        <v>0.247</v>
-      </c>
-      <c r="J25" s="129" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="94">
-        <v>135</v>
-      </c>
-      <c r="C26" s="94">
-        <v>15</v>
-      </c>
-      <c r="D26" s="96">
-        <v>20.3</v>
-      </c>
-      <c r="E26" s="99">
-        <v>1</v>
-      </c>
-      <c r="F26" s="122">
-        <v>0.41249999999999998</v>
-      </c>
-      <c r="G26" s="126">
-        <v>0.50700000000000001</v>
-      </c>
-      <c r="H26" s="97">
-        <v>0.1</v>
-      </c>
-      <c r="I26" s="94">
-        <v>1</v>
-      </c>
-      <c r="J26" s="94" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="94">
-        <v>112.5</v>
-      </c>
-      <c r="C27" s="94">
-        <v>27</v>
-      </c>
-      <c r="D27" s="96">
-        <v>13.5</v>
-      </c>
-      <c r="E27" s="99">
-        <v>10</v>
-      </c>
-      <c r="F27" s="122">
-        <v>0.45</v>
-      </c>
-      <c r="G27" s="126">
-        <v>0.58099999999999996</v>
-      </c>
-      <c r="H27" s="97">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="I27" s="94">
-        <v>0.12</v>
-      </c>
-      <c r="J27" s="94" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="105">
-        <v>90</v>
-      </c>
-      <c r="C28" s="105">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="D28" s="106">
-        <v>13.5</v>
-      </c>
-      <c r="E28" s="107">
-        <v>9</v>
-      </c>
-      <c r="F28" s="123">
-        <v>0.45124999999999998</v>
-      </c>
-      <c r="G28" s="127">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="H28" s="108">
-        <v>0.05</v>
-      </c>
-      <c r="I28" s="105">
-        <v>0</v>
-      </c>
-      <c r="J28" s="105" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="94">
-        <v>135</v>
-      </c>
-      <c r="C29" s="94">
-        <v>18.8</v>
-      </c>
-      <c r="D29" s="96">
-        <v>16.2</v>
-      </c>
-      <c r="E29" s="99">
-        <v>2</v>
-      </c>
-      <c r="F29" s="122">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="G29" s="126">
-        <v>0.61099999999999999</v>
-      </c>
-      <c r="H29" s="97">
-        <v>0.11</v>
-      </c>
-      <c r="I29" s="94">
-        <v>0.42</v>
-      </c>
-      <c r="J29" s="94" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="94">
-        <v>112.5</v>
-      </c>
-      <c r="C30" s="94">
-        <v>22.5</v>
-      </c>
-      <c r="D30" s="96">
-        <v>16.2</v>
-      </c>
-      <c r="E30" s="99">
-        <v>6</v>
-      </c>
-      <c r="F30" s="122">
-        <v>0.54749999999999999</v>
-      </c>
-      <c r="G30" s="126">
-        <v>0.77300000000000002</v>
-      </c>
-      <c r="H30" s="97">
-        <v>0.05</v>
-      </c>
-      <c r="I30" s="94">
-        <v>0.193</v>
-      </c>
-      <c r="J30" s="94" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="100">
-        <v>90</v>
-      </c>
-      <c r="C31" s="100">
-        <v>22.5</v>
-      </c>
-      <c r="D31" s="101">
-        <v>20.3</v>
-      </c>
-      <c r="E31" s="102">
-        <v>5</v>
-      </c>
-      <c r="F31" s="124">
-        <v>0.66</v>
-      </c>
-      <c r="G31" s="128">
-        <v>1</v>
-      </c>
-      <c r="H31" s="103">
-        <v>0</v>
-      </c>
-      <c r="I31" s="100">
-        <v>0.222</v>
-      </c>
-      <c r="J31" s="100" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="24" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="91" t="s">
+      <c r="B34" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="C34" s="91" t="s">
+      <c r="C34" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="91" t="s">
+      <c r="D34" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="E34" s="98" t="s">
-        <v>189</v>
-      </c>
-      <c r="F34" s="91" t="s">
+      <c r="E34" s="94" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" s="87" t="s">
+        <v>168</v>
+      </c>
+      <c r="G34" s="113" t="s">
         <v>169</v>
       </c>
-      <c r="G34" s="117" t="s">
+      <c r="H34" s="108" t="s">
         <v>170</v>
       </c>
-      <c r="H34" s="112" t="s">
+      <c r="I34" s="107" t="s">
         <v>171</v>
       </c>
-      <c r="I34" s="111" t="s">
+      <c r="J34" s="89" t="s">
         <v>172</v>
       </c>
-      <c r="J34" s="93" t="s">
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B35" s="96">
+        <v>90</v>
+      </c>
+      <c r="C35" s="96">
+        <v>22.5</v>
+      </c>
+      <c r="D35" s="97">
+        <v>20.3</v>
+      </c>
+      <c r="E35" s="98">
+        <v>5</v>
+      </c>
+      <c r="F35" s="99">
+        <v>0.66</v>
+      </c>
+      <c r="G35" s="114">
+        <v>1</v>
+      </c>
+      <c r="H35" s="111">
+        <v>0</v>
+      </c>
+      <c r="I35" s="99">
+        <v>0.222</v>
+      </c>
+      <c r="J35" s="96" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B36" s="90">
+        <v>112.5</v>
+      </c>
+      <c r="C36" s="90">
+        <v>22.5</v>
+      </c>
+      <c r="D36" s="92">
+        <v>16.2</v>
+      </c>
+      <c r="E36" s="95">
+        <v>6</v>
+      </c>
+      <c r="F36" s="93">
+        <v>0.54749999999999999</v>
+      </c>
+      <c r="G36" s="115">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="H36" s="110">
+        <v>0.05</v>
+      </c>
+      <c r="I36" s="93">
+        <v>0.193</v>
+      </c>
+      <c r="J36" s="90" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B37" s="101">
+        <v>90</v>
+      </c>
+      <c r="C37" s="101">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D37" s="102">
+        <v>13.5</v>
+      </c>
+      <c r="E37" s="103">
+        <v>9</v>
+      </c>
+      <c r="F37" s="104">
+        <v>0.45124999999999998</v>
+      </c>
+      <c r="G37" s="116">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="H37" s="109">
+        <v>0.05</v>
+      </c>
+      <c r="I37" s="104">
+        <v>0</v>
+      </c>
+      <c r="J37" s="101" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B38" s="90">
+        <v>112.5</v>
+      </c>
+      <c r="C38" s="90">
+        <v>27</v>
+      </c>
+      <c r="D38" s="92">
+        <v>13.5</v>
+      </c>
+      <c r="E38" s="95">
+        <v>10</v>
+      </c>
+      <c r="F38" s="93">
+        <v>0.45</v>
+      </c>
+      <c r="G38" s="115">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="H38" s="110">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I38" s="93">
+        <v>0.12</v>
+      </c>
+      <c r="J38" s="90" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B39" s="90">
+        <v>135</v>
+      </c>
+      <c r="C39" s="90">
+        <v>15</v>
+      </c>
+      <c r="D39" s="92">
+        <v>20.3</v>
+      </c>
+      <c r="E39" s="95">
+        <v>1</v>
+      </c>
+      <c r="F39" s="93">
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="G39" s="115">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="H39" s="110">
+        <v>0.1</v>
+      </c>
+      <c r="I39" s="93">
+        <v>1</v>
+      </c>
+      <c r="J39" s="90" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B40" s="90">
+        <v>135</v>
+      </c>
+      <c r="C40" s="90">
+        <v>18.8</v>
+      </c>
+      <c r="D40" s="92">
+        <v>16.2</v>
+      </c>
+      <c r="E40" s="95">
+        <v>2</v>
+      </c>
+      <c r="F40" s="93">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="G40" s="115">
+        <v>0.61099999999999999</v>
+      </c>
+      <c r="H40" s="110">
+        <v>0.11</v>
+      </c>
+      <c r="I40" s="93">
+        <v>0.42</v>
+      </c>
+      <c r="J40" s="90" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" s="125">
+        <v>135</v>
+      </c>
+      <c r="C41" s="125">
+        <v>22.5</v>
+      </c>
+      <c r="D41" s="126">
+        <v>13.5</v>
+      </c>
+      <c r="E41" s="127">
+        <v>0</v>
+      </c>
+      <c r="F41" s="128" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="100">
-        <v>90</v>
-      </c>
-      <c r="C35" s="100">
+      <c r="G41" s="132">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H41" s="133">
+        <v>0.15</v>
+      </c>
+      <c r="I41" s="128">
+        <v>0.247</v>
+      </c>
+      <c r="J41" s="125" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" s="90">
+        <v>135</v>
+      </c>
+      <c r="C42" s="90">
+        <v>27</v>
+      </c>
+      <c r="D42" s="92">
+        <v>11.25</v>
+      </c>
+      <c r="E42" s="95">
+        <v>3</v>
+      </c>
+      <c r="F42" s="93">
+        <v>0.31125000000000003</v>
+      </c>
+      <c r="G42" s="115">
+        <v>0.308</v>
+      </c>
+      <c r="H42" s="110">
+        <v>0.2</v>
+      </c>
+      <c r="I42" s="93">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="J42" s="90" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B43" s="90">
+        <v>162</v>
+      </c>
+      <c r="C43" s="90">
+        <v>18.8</v>
+      </c>
+      <c r="D43" s="92">
+        <v>13.5</v>
+      </c>
+      <c r="E43" s="95">
+        <v>11</v>
+      </c>
+      <c r="F43" s="93">
+        <v>0.30249999999999999</v>
+      </c>
+      <c r="G43" s="115">
+        <v>0.29099999999999998</v>
+      </c>
+      <c r="H43" s="110">
+        <v>0.27</v>
+      </c>
+      <c r="I43" s="93">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="J43" s="90" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="90">
+        <v>135</v>
+      </c>
+      <c r="C44" s="90">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D44" s="92">
+        <v>9</v>
+      </c>
+      <c r="E44" s="95">
+        <v>4</v>
+      </c>
+      <c r="F44" s="93">
+        <v>0.24374999999999999</v>
+      </c>
+      <c r="G44" s="115">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H44" s="110">
+        <v>0.35</v>
+      </c>
+      <c r="I44" s="93">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="J44" s="90" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B45" s="90">
+        <v>162</v>
+      </c>
+      <c r="C45" s="90">
         <v>22.5</v>
       </c>
-      <c r="D35" s="101">
-        <v>20.3</v>
-      </c>
-      <c r="E35" s="102">
-        <v>5</v>
-      </c>
-      <c r="F35" s="103">
-        <v>0.66</v>
-      </c>
-      <c r="G35" s="118">
+      <c r="D45" s="92">
+        <v>11.3</v>
+      </c>
+      <c r="E45" s="95">
+        <v>7</v>
+      </c>
+      <c r="F45" s="93">
+        <v>0.22875000000000001</v>
+      </c>
+      <c r="G45" s="115">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="H45" s="110">
+        <v>0.4</v>
+      </c>
+      <c r="I45" s="93">
+        <v>0.35</v>
+      </c>
+      <c r="J45" s="90" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B46" s="90">
+        <v>202.5</v>
+      </c>
+      <c r="C46" s="90">
+        <v>15</v>
+      </c>
+      <c r="D46" s="92">
+        <v>13.5</v>
+      </c>
+      <c r="E46" s="95">
+        <v>12</v>
+      </c>
+      <c r="F46" s="93" t="s">
+        <v>186</v>
+      </c>
+      <c r="G46" s="115">
+        <v>0</v>
+      </c>
+      <c r="H46" s="110">
+        <v>0.65</v>
+      </c>
+      <c r="I46" s="93">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J46" s="90" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="90">
+        <v>202.5</v>
+      </c>
+      <c r="C47" s="90">
+        <v>22.5</v>
+      </c>
+      <c r="D47" s="92">
+        <v>9</v>
+      </c>
+      <c r="E47" s="95">
+        <v>8</v>
+      </c>
+      <c r="F47" s="93">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="G47" s="115">
+        <v>0.374</v>
+      </c>
+      <c r="H47" s="112">
         <v>1</v>
       </c>
-      <c r="H35" s="115">
-        <v>0</v>
-      </c>
-      <c r="I35" s="103">
-        <v>0.222</v>
-      </c>
-      <c r="J35" s="100" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="94">
-        <v>112.5</v>
-      </c>
-      <c r="C36" s="94">
-        <v>22.5</v>
-      </c>
-      <c r="D36" s="96">
-        <v>16.2</v>
-      </c>
-      <c r="E36" s="99">
-        <v>6</v>
-      </c>
-      <c r="F36" s="97">
-        <v>0.54749999999999999</v>
-      </c>
-      <c r="G36" s="119">
-        <v>0.77300000000000002</v>
-      </c>
-      <c r="H36" s="114">
-        <v>0.05</v>
-      </c>
-      <c r="I36" s="97">
-        <v>0.193</v>
-      </c>
-      <c r="J36" s="94" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="105">
-        <v>90</v>
-      </c>
-      <c r="C37" s="105">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="D37" s="106">
-        <v>13.5</v>
-      </c>
-      <c r="E37" s="107">
-        <v>9</v>
-      </c>
-      <c r="F37" s="108">
-        <v>0.45124999999999998</v>
-      </c>
-      <c r="G37" s="120">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="H37" s="113">
-        <v>0.05</v>
-      </c>
-      <c r="I37" s="108">
-        <v>0</v>
-      </c>
-      <c r="J37" s="105" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="94">
-        <v>112.5</v>
-      </c>
-      <c r="C38" s="94">
-        <v>27</v>
-      </c>
-      <c r="D38" s="96">
-        <v>13.5</v>
-      </c>
-      <c r="E38" s="99">
-        <v>10</v>
-      </c>
-      <c r="F38" s="97">
-        <v>0.45</v>
-      </c>
-      <c r="G38" s="119">
-        <v>0.58099999999999996</v>
-      </c>
-      <c r="H38" s="114">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="I38" s="97">
-        <v>0.12</v>
-      </c>
-      <c r="J38" s="94" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="94">
-        <v>135</v>
-      </c>
-      <c r="C39" s="94">
-        <v>15</v>
-      </c>
-      <c r="D39" s="96">
-        <v>20.3</v>
-      </c>
-      <c r="E39" s="99">
-        <v>1</v>
-      </c>
-      <c r="F39" s="97">
-        <v>0.41249999999999998</v>
-      </c>
-      <c r="G39" s="119">
-        <v>0.50700000000000001</v>
-      </c>
-      <c r="H39" s="114">
-        <v>0.1</v>
-      </c>
-      <c r="I39" s="97">
-        <v>1</v>
-      </c>
-      <c r="J39" s="94" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B40" s="94">
-        <v>135</v>
-      </c>
-      <c r="C40" s="94">
-        <v>18.8</v>
-      </c>
-      <c r="D40" s="96">
-        <v>16.2</v>
-      </c>
-      <c r="E40" s="99">
-        <v>2</v>
-      </c>
-      <c r="F40" s="97">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="G40" s="119">
-        <v>0.61099999999999999</v>
-      </c>
-      <c r="H40" s="114">
-        <v>0.11</v>
-      </c>
-      <c r="I40" s="97">
-        <v>0.42</v>
-      </c>
-      <c r="J40" s="94" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B41" s="129">
-        <v>135</v>
-      </c>
-      <c r="C41" s="129">
-        <v>22.5</v>
-      </c>
-      <c r="D41" s="130">
-        <v>13.5</v>
-      </c>
-      <c r="E41" s="131">
-        <v>0</v>
-      </c>
-      <c r="F41" s="132" t="s">
-        <v>174</v>
-      </c>
-      <c r="G41" s="136">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="H41" s="137">
-        <v>0.15</v>
-      </c>
-      <c r="I41" s="132">
-        <v>0.247</v>
-      </c>
-      <c r="J41" s="129" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="94">
-        <v>135</v>
-      </c>
-      <c r="C42" s="94">
-        <v>27</v>
-      </c>
-      <c r="D42" s="96">
-        <v>11.25</v>
-      </c>
-      <c r="E42" s="99">
-        <v>3</v>
-      </c>
-      <c r="F42" s="97">
-        <v>0.31125000000000003</v>
-      </c>
-      <c r="G42" s="119">
-        <v>0.308</v>
-      </c>
-      <c r="H42" s="114">
-        <v>0.2</v>
-      </c>
-      <c r="I42" s="97">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="J42" s="94" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B43" s="94">
-        <v>162</v>
-      </c>
-      <c r="C43" s="94">
-        <v>18.8</v>
-      </c>
-      <c r="D43" s="96">
-        <v>13.5</v>
-      </c>
-      <c r="E43" s="99">
-        <v>11</v>
-      </c>
-      <c r="F43" s="97">
-        <v>0.30249999999999999</v>
-      </c>
-      <c r="G43" s="119">
-        <v>0.29099999999999998</v>
-      </c>
-      <c r="H43" s="114">
-        <v>0.27</v>
-      </c>
-      <c r="I43" s="97">
-        <v>0.40899999999999997</v>
-      </c>
-      <c r="J43" s="94" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="94">
-        <v>135</v>
-      </c>
-      <c r="C44" s="94">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="D44" s="96">
-        <v>9</v>
-      </c>
-      <c r="E44" s="99">
-        <v>4</v>
-      </c>
-      <c r="F44" s="97">
-        <v>0.24374999999999999</v>
-      </c>
-      <c r="G44" s="119">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="H44" s="114">
-        <v>0.35</v>
-      </c>
-      <c r="I44" s="97">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="J44" s="94" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="94">
-        <v>162</v>
-      </c>
-      <c r="C45" s="94">
-        <v>22.5</v>
-      </c>
-      <c r="D45" s="96">
-        <v>11.3</v>
-      </c>
-      <c r="E45" s="99">
-        <v>7</v>
-      </c>
-      <c r="F45" s="97">
-        <v>0.22875000000000001</v>
-      </c>
-      <c r="G45" s="119">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="H45" s="114">
-        <v>0.4</v>
-      </c>
-      <c r="I45" s="97">
-        <v>0.35</v>
-      </c>
-      <c r="J45" s="94" t="s">
+      <c r="I47" s="93">
+        <v>0.499</v>
+      </c>
+      <c r="J47" s="90" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="94">
-        <v>202.5</v>
-      </c>
-      <c r="C46" s="94">
-        <v>15</v>
-      </c>
-      <c r="D46" s="96">
-        <v>13.5</v>
-      </c>
-      <c r="E46" s="99">
-        <v>12</v>
-      </c>
-      <c r="F46" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="G46" s="119">
-        <v>0</v>
-      </c>
-      <c r="H46" s="114">
-        <v>0.65</v>
-      </c>
-      <c r="I46" s="97">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="J46" s="94" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="94">
-        <v>202.5</v>
-      </c>
-      <c r="C47" s="94">
-        <v>22.5</v>
-      </c>
-      <c r="D47" s="96">
-        <v>9</v>
-      </c>
-      <c r="E47" s="99">
-        <v>8</v>
-      </c>
-      <c r="F47" s="97">
-        <v>0.34499999999999997</v>
-      </c>
-      <c r="G47" s="119">
-        <v>0.374</v>
-      </c>
-      <c r="H47" s="116">
-        <v>1</v>
-      </c>
-      <c r="I47" s="97">
-        <v>0.499</v>
-      </c>
-      <c r="J47" s="94" t="s">
-        <v>183</v>
-      </c>
       <c r="M47" t="s">
+        <v>192</v>
+      </c>
+      <c r="N47" t="s">
+        <v>166</v>
+      </c>
+      <c r="O47" t="s">
         <v>193</v>
-      </c>
-      <c r="N47" t="s">
-        <v>167</v>
-      </c>
-      <c r="O47" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.25">
@@ -7214,187 +7556,187 @@
     </row>
     <row r="49" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B50" s="91" t="s">
+      <c r="B50" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="C50" s="91" t="s">
+      <c r="C50" s="87" t="s">
         <v>90</v>
       </c>
-      <c r="D50" s="91" t="s">
+      <c r="D50" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="E50" s="98" t="s">
-        <v>189</v>
-      </c>
-      <c r="F50" s="91" t="s">
+      <c r="E50" s="94" t="s">
+        <v>188</v>
+      </c>
+      <c r="F50" s="87" t="s">
+        <v>168</v>
+      </c>
+      <c r="G50" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="G50" s="92" t="s">
+      <c r="H50" s="106" t="s">
         <v>170</v>
       </c>
-      <c r="H50" s="110" t="s">
+      <c r="I50" s="108" t="s">
         <v>171</v>
       </c>
-      <c r="I50" s="112" t="s">
+      <c r="J50" s="107" t="s">
         <v>172</v>
       </c>
-      <c r="J50" s="111" t="s">
+      <c r="L50" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="M50" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="N50" s="87" t="s">
+        <v>91</v>
+      </c>
+      <c r="O50" s="94" t="s">
+        <v>188</v>
+      </c>
+      <c r="P50" s="136" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B51" s="125">
+        <v>135</v>
+      </c>
+      <c r="C51" s="125">
+        <v>22.5</v>
+      </c>
+      <c r="D51" s="126">
+        <v>13.5</v>
+      </c>
+      <c r="E51" s="127">
+        <v>0</v>
+      </c>
+      <c r="F51" s="128" t="s">
         <v>173</v>
       </c>
-      <c r="L50" s="91" t="s">
-        <v>89</v>
-      </c>
-      <c r="M50" s="91" t="s">
-        <v>90</v>
-      </c>
-      <c r="N50" s="91" t="s">
-        <v>91</v>
-      </c>
-      <c r="O50" s="98" t="s">
-        <v>189</v>
-      </c>
-      <c r="P50" s="140" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="51" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B51" s="129">
-        <v>135</v>
-      </c>
-      <c r="C51" s="129">
-        <v>22.5</v>
-      </c>
-      <c r="D51" s="130">
-        <v>13.5</v>
-      </c>
-      <c r="E51" s="131">
-        <v>0</v>
-      </c>
-      <c r="F51" s="132" t="s">
+      <c r="G51" s="129">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="H51" s="126">
+        <v>0.15</v>
+      </c>
+      <c r="I51" s="133">
+        <v>0.247</v>
+      </c>
+      <c r="J51" s="128" t="s">
         <v>174</v>
       </c>
-      <c r="G51" s="133">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="H51" s="130">
-        <v>0.15</v>
-      </c>
-      <c r="I51" s="137">
-        <v>0.247</v>
-      </c>
-      <c r="J51" s="132" t="s">
-        <v>175</v>
-      </c>
-      <c r="L51" s="138">
+      <c r="L51" s="134">
         <f>B51*$O$48</f>
         <v>157.19999999999999</v>
       </c>
-      <c r="M51" s="138">
+      <c r="M51" s="134">
         <f>C51*$O$48</f>
         <v>26.2</v>
       </c>
-      <c r="N51" s="138">
+      <c r="N51" s="134">
         <f>D51*$O$48</f>
         <v>15.719999999999999</v>
       </c>
-      <c r="O51" s="139">
+      <c r="O51" s="135">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B52" s="94">
+      <c r="B52" s="90">
         <v>135</v>
       </c>
-      <c r="C52" s="94">
+      <c r="C52" s="90">
         <v>15</v>
       </c>
-      <c r="D52" s="96">
+      <c r="D52" s="92">
         <v>20.3</v>
       </c>
-      <c r="E52" s="99">
+      <c r="E52" s="95">
         <v>1</v>
       </c>
-      <c r="F52" s="97">
+      <c r="F52" s="93">
         <v>0.41249999999999998</v>
       </c>
-      <c r="G52" s="95">
+      <c r="G52" s="91">
         <v>0.50700000000000001</v>
       </c>
-      <c r="H52" s="96">
+      <c r="H52" s="92">
         <v>0.1</v>
       </c>
-      <c r="I52" s="114">
+      <c r="I52" s="110">
         <v>1</v>
       </c>
-      <c r="J52" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="L52" s="138">
+      <c r="J52" s="93" t="s">
+        <v>175</v>
+      </c>
+      <c r="L52" s="134">
         <f t="shared" ref="L52:L63" si="0">B52*$O$48</f>
         <v>157.19999999999999</v>
       </c>
-      <c r="M52" s="138">
+      <c r="M52" s="134">
         <f t="shared" ref="M52:M63" si="1">C52*$O$48</f>
         <v>17.466666666666665</v>
       </c>
-      <c r="N52" s="138">
+      <c r="N52" s="134">
         <f t="shared" ref="N52:N63" si="2">D52*$O$48</f>
         <v>23.638222222222222</v>
       </c>
-      <c r="O52" s="139">
+      <c r="O52" s="135">
         <v>1</v>
       </c>
       <c r="T52" s="20"/>
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B53" s="94">
+      <c r="B53" s="90">
         <v>135</v>
       </c>
-      <c r="C53" s="94">
+      <c r="C53" s="90">
         <v>18.8</v>
       </c>
-      <c r="D53" s="96">
+      <c r="D53" s="92">
         <v>16.2</v>
       </c>
-      <c r="E53" s="99">
+      <c r="E53" s="95">
         <v>2</v>
       </c>
-      <c r="F53" s="97">
+      <c r="F53" s="93">
         <v>0.46500000000000002</v>
       </c>
-      <c r="G53" s="95">
+      <c r="G53" s="91">
         <v>0.61099999999999999</v>
       </c>
-      <c r="H53" s="96">
+      <c r="H53" s="92">
         <v>0.11</v>
       </c>
-      <c r="I53" s="114">
+      <c r="I53" s="110">
         <v>0.42</v>
       </c>
-      <c r="J53" s="97" t="s">
-        <v>177</v>
-      </c>
-      <c r="L53" s="138">
+      <c r="J53" s="93" t="s">
+        <v>176</v>
+      </c>
+      <c r="L53" s="134">
         <f t="shared" si="0"/>
         <v>157.19999999999999</v>
       </c>
-      <c r="M53" s="138">
+      <c r="M53" s="134">
         <f t="shared" si="1"/>
         <v>21.891555555555556</v>
       </c>
-      <c r="N53" s="138">
+      <c r="N53" s="134">
         <f t="shared" si="2"/>
         <v>18.863999999999997</v>
       </c>
-      <c r="O53" s="139">
+      <c r="O53" s="135">
         <v>2</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="S53" s="3">
         <v>0.5</v>
@@ -7402,50 +7744,50 @@
       <c r="T53" s="3"/>
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B54" s="94">
+      <c r="B54" s="90">
         <v>135</v>
       </c>
-      <c r="C54" s="94">
+      <c r="C54" s="90">
         <v>27</v>
       </c>
-      <c r="D54" s="96">
+      <c r="D54" s="92">
         <v>11.25</v>
       </c>
-      <c r="E54" s="99">
+      <c r="E54" s="95">
         <v>3</v>
       </c>
-      <c r="F54" s="97">
+      <c r="F54" s="93">
         <v>0.31125000000000003</v>
       </c>
-      <c r="G54" s="95">
+      <c r="G54" s="91">
         <v>0.308</v>
       </c>
-      <c r="H54" s="96">
+      <c r="H54" s="92">
         <v>0.2</v>
       </c>
-      <c r="I54" s="114">
+      <c r="I54" s="110">
         <v>0.26400000000000001</v>
       </c>
-      <c r="J54" s="97" t="s">
-        <v>178</v>
-      </c>
-      <c r="L54" s="138">
+      <c r="J54" s="93" t="s">
+        <v>177</v>
+      </c>
+      <c r="L54" s="134">
         <f t="shared" si="0"/>
         <v>157.19999999999999</v>
       </c>
-      <c r="M54" s="138">
+      <c r="M54" s="134">
         <f t="shared" si="1"/>
         <v>31.439999999999998</v>
       </c>
-      <c r="N54" s="138">
+      <c r="N54" s="134">
         <f t="shared" si="2"/>
         <v>13.1</v>
       </c>
-      <c r="O54" s="139">
+      <c r="O54" s="135">
         <v>3</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="S54" s="3">
         <v>4.5</v>
@@ -7455,152 +7797,152 @@
       </c>
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B55" s="94">
+      <c r="B55" s="90">
         <v>135</v>
       </c>
-      <c r="C55" s="94">
+      <c r="C55" s="90">
         <v>33.799999999999997</v>
       </c>
-      <c r="D55" s="96">
+      <c r="D55" s="92">
         <v>9</v>
       </c>
-      <c r="E55" s="99">
+      <c r="E55" s="95">
         <v>4</v>
       </c>
-      <c r="F55" s="97">
+      <c r="F55" s="93">
         <v>0.24374999999999999</v>
       </c>
-      <c r="G55" s="95">
+      <c r="G55" s="91">
         <v>0.17499999999999999</v>
       </c>
-      <c r="H55" s="96">
+      <c r="H55" s="92">
         <v>0.35</v>
       </c>
-      <c r="I55" s="114">
+      <c r="I55" s="110">
         <v>0.41199999999999998</v>
       </c>
-      <c r="J55" s="97" t="s">
-        <v>179</v>
-      </c>
-      <c r="L55" s="138">
+      <c r="J55" s="93" t="s">
+        <v>178</v>
+      </c>
+      <c r="L55" s="134">
         <f t="shared" si="0"/>
         <v>157.19999999999999</v>
       </c>
-      <c r="M55" s="138">
+      <c r="M55" s="134">
         <f t="shared" si="1"/>
         <v>39.358222222222217</v>
       </c>
-      <c r="N55" s="138">
+      <c r="N55" s="134">
         <f t="shared" si="2"/>
         <v>10.48</v>
       </c>
-      <c r="O55" s="139">
+      <c r="O55" s="135">
         <v>4</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="S55" s="3">
         <v>30</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B56" s="100">
+      <c r="B56" s="96">
         <v>90</v>
       </c>
-      <c r="C56" s="100">
+      <c r="C56" s="96">
         <v>22.5</v>
       </c>
-      <c r="D56" s="101">
+      <c r="D56" s="97">
         <v>20.3</v>
       </c>
-      <c r="E56" s="102">
+      <c r="E56" s="98">
         <v>5</v>
       </c>
-      <c r="F56" s="103">
+      <c r="F56" s="99">
         <v>0.66</v>
       </c>
-      <c r="G56" s="104">
+      <c r="G56" s="100">
         <v>1</v>
       </c>
-      <c r="H56" s="101">
+      <c r="H56" s="97">
         <v>0</v>
       </c>
-      <c r="I56" s="115">
+      <c r="I56" s="111">
         <v>0.222</v>
       </c>
-      <c r="J56" s="103" t="s">
-        <v>180</v>
-      </c>
-      <c r="L56" s="138">
+      <c r="J56" s="99" t="s">
+        <v>179</v>
+      </c>
+      <c r="L56" s="134">
         <f t="shared" si="0"/>
         <v>104.8</v>
       </c>
-      <c r="M56" s="138">
+      <c r="M56" s="134">
         <f t="shared" si="1"/>
         <v>26.2</v>
       </c>
-      <c r="N56" s="138">
+      <c r="N56" s="134">
         <f t="shared" si="2"/>
         <v>23.638222222222222</v>
       </c>
-      <c r="O56" s="139">
+      <c r="O56" s="135">
         <v>5</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="S56" s="3">
         <v>3.0832999999999999</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B57" s="94">
+      <c r="B57" s="90">
         <v>112.5</v>
       </c>
-      <c r="C57" s="94">
+      <c r="C57" s="90">
         <v>22.5</v>
       </c>
-      <c r="D57" s="96">
+      <c r="D57" s="92">
         <v>16.2</v>
       </c>
-      <c r="E57" s="99">
+      <c r="E57" s="95">
         <v>6</v>
       </c>
-      <c r="F57" s="97">
+      <c r="F57" s="93">
         <v>0.54749999999999999</v>
       </c>
-      <c r="G57" s="95">
+      <c r="G57" s="91">
         <v>0.77300000000000002</v>
       </c>
-      <c r="H57" s="96">
+      <c r="H57" s="92">
         <v>0.05</v>
       </c>
-      <c r="I57" s="114">
+      <c r="I57" s="110">
         <v>0.193</v>
       </c>
-      <c r="J57" s="97" t="s">
-        <v>181</v>
-      </c>
-      <c r="L57" s="138">
+      <c r="J57" s="93" t="s">
+        <v>180</v>
+      </c>
+      <c r="L57" s="134">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="M57" s="138">
+      <c r="M57" s="134">
         <f t="shared" si="1"/>
         <v>26.2</v>
       </c>
-      <c r="N57" s="138">
+      <c r="N57" s="134">
         <f t="shared" si="2"/>
         <v>18.863999999999997</v>
       </c>
-      <c r="O57" s="139">
+      <c r="O57" s="135">
         <v>6</v>
       </c>
       <c r="R57" s="3"/>
@@ -7608,50 +7950,50 @@
         <v>3.0855000000000001</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B58" s="94">
+      <c r="B58" s="90">
         <v>162</v>
       </c>
-      <c r="C58" s="94">
+      <c r="C58" s="90">
         <v>22.5</v>
       </c>
-      <c r="D58" s="96">
+      <c r="D58" s="92">
         <v>11.3</v>
       </c>
-      <c r="E58" s="99">
+      <c r="E58" s="95">
         <v>7</v>
       </c>
-      <c r="F58" s="97">
+      <c r="F58" s="93">
         <v>0.22875000000000001</v>
       </c>
-      <c r="G58" s="95">
+      <c r="G58" s="91">
         <v>0.14499999999999999</v>
       </c>
-      <c r="H58" s="96">
+      <c r="H58" s="92">
         <v>0.4</v>
       </c>
-      <c r="I58" s="114">
+      <c r="I58" s="110">
         <v>0.35</v>
       </c>
-      <c r="J58" s="97" t="s">
-        <v>182</v>
-      </c>
-      <c r="L58" s="138">
+      <c r="J58" s="93" t="s">
+        <v>181</v>
+      </c>
+      <c r="L58" s="134">
         <f t="shared" si="0"/>
         <v>188.64</v>
       </c>
-      <c r="M58" s="138">
+      <c r="M58" s="134">
         <f t="shared" si="1"/>
         <v>26.2</v>
       </c>
-      <c r="N58" s="138">
+      <c r="N58" s="134">
         <f t="shared" si="2"/>
         <v>13.158222222222223</v>
       </c>
-      <c r="O58" s="139">
+      <c r="O58" s="135">
         <v>7</v>
       </c>
       <c r="R58" s="3"/>
@@ -7659,423 +8001,442 @@
         <v>3.0832999999999999</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B59" s="94">
+      <c r="B59" s="90">
         <v>202.5</v>
       </c>
-      <c r="C59" s="94">
+      <c r="C59" s="90">
         <v>22.5</v>
       </c>
-      <c r="D59" s="96">
+      <c r="D59" s="92">
         <v>9</v>
       </c>
-      <c r="E59" s="99">
+      <c r="E59" s="95">
         <v>8</v>
       </c>
-      <c r="F59" s="97">
+      <c r="F59" s="93">
         <v>0.34499999999999997</v>
       </c>
-      <c r="G59" s="95">
+      <c r="G59" s="91">
         <v>0.374</v>
       </c>
-      <c r="H59" s="96">
+      <c r="H59" s="92">
         <v>1</v>
       </c>
-      <c r="I59" s="114">
+      <c r="I59" s="110">
         <v>0.499</v>
       </c>
-      <c r="J59" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="L59" s="138">
+      <c r="J59" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="L59" s="134">
         <f t="shared" si="0"/>
         <v>235.79999999999998</v>
       </c>
-      <c r="M59" s="138">
+      <c r="M59" s="134">
         <f t="shared" si="1"/>
         <v>26.2</v>
       </c>
-      <c r="N59" s="138">
+      <c r="N59" s="134">
         <f t="shared" si="2"/>
         <v>10.48</v>
       </c>
-      <c r="O59" s="139">
+      <c r="O59" s="135">
         <v>8</v>
       </c>
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B60" s="105">
+      <c r="B60" s="101">
         <v>90</v>
       </c>
-      <c r="C60" s="105">
+      <c r="C60" s="101">
         <v>33.799999999999997</v>
       </c>
-      <c r="D60" s="106">
+      <c r="D60" s="102">
         <v>13.5</v>
       </c>
-      <c r="E60" s="107">
+      <c r="E60" s="103">
         <v>9</v>
       </c>
-      <c r="F60" s="108">
+      <c r="F60" s="104">
         <v>0.45124999999999998</v>
       </c>
-      <c r="G60" s="109">
+      <c r="G60" s="105">
         <v>0.58399999999999996</v>
       </c>
-      <c r="H60" s="106">
+      <c r="H60" s="102">
         <v>0.05</v>
       </c>
-      <c r="I60" s="113">
+      <c r="I60" s="109">
         <v>0</v>
       </c>
-      <c r="J60" s="108" t="s">
-        <v>184</v>
-      </c>
-      <c r="L60" s="138">
+      <c r="J60" s="104" t="s">
+        <v>183</v>
+      </c>
+      <c r="L60" s="134">
         <f t="shared" si="0"/>
         <v>104.8</v>
       </c>
-      <c r="M60" s="138">
+      <c r="M60" s="134">
         <f t="shared" si="1"/>
         <v>39.358222222222217</v>
       </c>
-      <c r="N60" s="138">
+      <c r="N60" s="134">
         <f t="shared" si="2"/>
         <v>15.719999999999999</v>
       </c>
-      <c r="O60" s="139">
+      <c r="O60" s="135">
         <v>9</v>
       </c>
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B61" s="94">
+      <c r="B61" s="90">
         <v>112.5</v>
       </c>
-      <c r="C61" s="94">
+      <c r="C61" s="90">
         <v>27</v>
       </c>
-      <c r="D61" s="96">
+      <c r="D61" s="92">
         <v>13.5</v>
       </c>
-      <c r="E61" s="99">
+      <c r="E61" s="95">
         <v>10</v>
       </c>
-      <c r="F61" s="97">
+      <c r="F61" s="93">
         <v>0.45</v>
       </c>
-      <c r="G61" s="95">
+      <c r="G61" s="91">
         <v>0.58099999999999996</v>
       </c>
-      <c r="H61" s="96">
+      <c r="H61" s="92">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I61" s="114">
+      <c r="I61" s="110">
         <v>0.12</v>
       </c>
-      <c r="J61" s="97" t="s">
-        <v>185</v>
-      </c>
-      <c r="L61" s="138">
+      <c r="J61" s="93" t="s">
+        <v>184</v>
+      </c>
+      <c r="L61" s="134">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="M61" s="138">
+      <c r="M61" s="134">
         <f t="shared" si="1"/>
         <v>31.439999999999998</v>
       </c>
-      <c r="N61" s="138">
+      <c r="N61" s="134">
         <f t="shared" si="2"/>
         <v>15.719999999999999</v>
       </c>
-      <c r="O61" s="139">
+      <c r="O61" s="135">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B62" s="94">
+    <row r="62" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="90">
         <v>162</v>
       </c>
-      <c r="C62" s="94">
+      <c r="C62" s="90">
         <v>18.8</v>
       </c>
-      <c r="D62" s="96">
+      <c r="D62" s="92">
         <v>13.5</v>
       </c>
-      <c r="E62" s="99">
+      <c r="E62" s="95">
         <v>11</v>
       </c>
-      <c r="F62" s="97">
+      <c r="F62" s="93">
         <v>0.30249999999999999</v>
       </c>
-      <c r="G62" s="95">
+      <c r="G62" s="91">
         <v>0.29099999999999998</v>
       </c>
-      <c r="H62" s="96">
+      <c r="H62" s="92">
         <v>0.27</v>
       </c>
-      <c r="I62" s="114">
+      <c r="I62" s="110">
         <v>0.40899999999999997</v>
       </c>
-      <c r="J62" s="97" t="s">
-        <v>186</v>
-      </c>
-      <c r="L62" s="138">
+      <c r="J62" s="93" t="s">
+        <v>185</v>
+      </c>
+      <c r="L62" s="134">
         <f t="shared" si="0"/>
         <v>188.64</v>
       </c>
-      <c r="M62" s="138">
+      <c r="M62" s="134">
         <f t="shared" si="1"/>
         <v>21.891555555555556</v>
       </c>
-      <c r="N62" s="138">
+      <c r="N62" s="134">
         <f t="shared" si="2"/>
         <v>15.719999999999999</v>
       </c>
-      <c r="O62" s="139">
+      <c r="O62" s="135">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="94">
+      <c r="S62" t="s">
+        <v>211</v>
+      </c>
+      <c r="T62" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" spans="2:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="90">
         <v>202.5</v>
       </c>
-      <c r="C63" s="94">
+      <c r="C63" s="90">
         <v>15</v>
       </c>
-      <c r="D63" s="96">
+      <c r="D63" s="92">
         <v>13.5</v>
       </c>
-      <c r="E63" s="99">
+      <c r="E63" s="95">
         <v>12</v>
       </c>
-      <c r="F63" s="97" t="s">
+      <c r="F63" s="93" t="s">
+        <v>186</v>
+      </c>
+      <c r="G63" s="91">
+        <v>0</v>
+      </c>
+      <c r="H63" s="92">
+        <v>0.65</v>
+      </c>
+      <c r="I63" s="112">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J63" s="93" t="s">
         <v>187</v>
       </c>
-      <c r="G63" s="95">
-        <v>0</v>
-      </c>
-      <c r="H63" s="96">
-        <v>0.65</v>
-      </c>
-      <c r="I63" s="116">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="J63" s="97" t="s">
-        <v>188</v>
-      </c>
-      <c r="L63" s="138">
+      <c r="L63" s="134">
         <f t="shared" si="0"/>
         <v>235.79999999999998</v>
       </c>
-      <c r="M63" s="138">
+      <c r="M63" s="134">
         <f t="shared" si="1"/>
         <v>17.466666666666665</v>
       </c>
-      <c r="N63" s="138">
+      <c r="N63" s="134">
         <f t="shared" si="2"/>
         <v>15.719999999999999</v>
       </c>
-      <c r="O63" s="139">
+      <c r="O63" s="135">
         <v>12</v>
       </c>
-    </row>
-    <row r="64" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="3:6" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C65" s="141" t="s">
+      <c r="Q63" s="137" t="s">
+        <v>196</v>
+      </c>
+      <c r="R63" s="138" t="s">
+        <v>210</v>
+      </c>
+      <c r="S63" s="137" t="s">
         <v>197</v>
       </c>
-      <c r="D65" s="142" t="s">
+      <c r="T63" s="137" t="s">
         <v>198</v>
       </c>
-      <c r="E65" s="141" t="s">
-        <v>199</v>
-      </c>
-      <c r="F65" s="141" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="66" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C66" s="141">
+    </row>
+    <row r="64" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q64" s="137">
         <v>0</v>
       </c>
-      <c r="D66" s="141">
+      <c r="R64" s="137">
         <v>31</v>
       </c>
-      <c r="E66" s="141">
+      <c r="S64" s="137">
         <v>0.80500000000000005</v>
       </c>
-      <c r="F66" s="144">
+      <c r="T64" s="140">
         <v>0.8044</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C67" s="141">
+    <row r="65" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q65" s="137">
         <v>1</v>
       </c>
-      <c r="D67" s="141">
+      <c r="R65" s="137">
         <v>53.5</v>
       </c>
-      <c r="E67" s="141">
+      <c r="S65" s="137">
         <v>0.32100000000000001</v>
       </c>
-      <c r="F67" s="144">
+      <c r="T65" s="140">
         <v>0.32140000000000002</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="141">
+    <row r="66" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F66">
+        <v>64</v>
+      </c>
+      <c r="Q66" s="137">
         <v>2</v>
       </c>
-      <c r="D68" s="141">
+      <c r="R66" s="137">
         <v>40.799999999999997</v>
       </c>
-      <c r="E68" s="141">
+      <c r="S66" s="137">
         <v>0.69399999999999995</v>
       </c>
-      <c r="F68" s="144">
+      <c r="T66" s="140">
         <v>0.69350000000000001</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C69" s="141">
+    <row r="67" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F67">
+        <v>72</v>
+      </c>
+      <c r="Q67" s="137">
         <v>3</v>
       </c>
-      <c r="D69" s="141">
+      <c r="R67" s="137">
         <v>22.6</v>
       </c>
-      <c r="E69" s="141">
+      <c r="S67" s="137">
         <v>0.79400000000000004</v>
       </c>
-      <c r="F69" s="144">
+      <c r="T67" s="140">
         <v>0.79330000000000001</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="141">
+    <row r="68" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F68">
+        <v>79</v>
+      </c>
+      <c r="Q68" s="137">
         <v>4</v>
       </c>
-      <c r="D70" s="141">
+      <c r="R68" s="137">
         <v>14.9</v>
       </c>
-      <c r="E70" s="143">
+      <c r="S68" s="139">
         <v>0.69899999999999995</v>
       </c>
-      <c r="F70" s="144">
+      <c r="T68" s="140">
         <v>0.69940000000000002</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C71" s="141">
+    <row r="69" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F69">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="137">
         <v>5</v>
       </c>
-      <c r="D71" s="141">
+      <c r="R69" s="137">
         <v>42</v>
       </c>
-      <c r="E71" s="143">
+      <c r="S69" s="139">
         <v>0.82099999999999995</v>
       </c>
-      <c r="F71" s="144">
+      <c r="T69" s="140">
         <v>0.82110000000000005</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="141">
+    <row r="70" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F70">
+        <f>SUM(F66:F69)</f>
+        <v>297</v>
+      </c>
+      <c r="Q70" s="137">
         <v>6</v>
       </c>
-      <c r="D72" s="141">
+      <c r="R70" s="137">
         <v>35.799999999999997</v>
       </c>
-      <c r="E72" s="143">
+      <c r="S70" s="139">
         <v>0.84</v>
       </c>
-      <c r="F72" s="144">
+      <c r="T70" s="140">
         <v>0.84109999999999996</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C73" s="141">
+    <row r="71" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q71" s="137">
         <v>7</v>
       </c>
-      <c r="D73" s="141">
+      <c r="R71" s="137">
         <v>26.6</v>
       </c>
-      <c r="E73" s="143">
+      <c r="S71" s="139">
         <v>0.73899999999999999</v>
       </c>
-      <c r="F73" s="144">
+      <c r="T71" s="140">
         <v>0.73960000000000004</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C74" s="141">
+    <row r="72" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q72" s="137">
         <v>8</v>
       </c>
-      <c r="D74" s="141">
+      <c r="R72" s="137">
         <v>21.8</v>
       </c>
-      <c r="E74" s="143">
+      <c r="S72" s="139">
         <v>0.64300000000000002</v>
       </c>
-      <c r="F74" s="144">
+      <c r="T72" s="140">
         <v>0.64270000000000005</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C75" s="141">
+    <row r="73" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q73" s="137">
         <v>9</v>
       </c>
-      <c r="D75" s="141">
+      <c r="R73" s="137">
         <v>21.8</v>
       </c>
-      <c r="E75" s="143">
+      <c r="S73" s="139">
         <v>0.96399999999999997</v>
       </c>
-      <c r="F75" s="144">
+      <c r="T73" s="140">
         <v>0.96419999999999995</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="141">
+    <row r="74" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q74" s="137">
         <v>10</v>
       </c>
-      <c r="D76" s="141">
+      <c r="R74" s="137">
         <v>26.6</v>
       </c>
-      <c r="E76" s="143">
+      <c r="S74" s="139">
         <v>0.88700000000000001</v>
       </c>
-      <c r="F76" s="144">
+      <c r="T74" s="140">
         <v>0.88749999999999996</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="141">
+    <row r="75" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q75" s="137">
         <v>11</v>
       </c>
-      <c r="D77" s="141">
+      <c r="R75" s="137">
         <v>35.799999999999997</v>
       </c>
-      <c r="E77" s="143">
+      <c r="S75" s="139">
         <v>0.70099999999999996</v>
       </c>
-      <c r="F77" s="144">
+      <c r="T75" s="140">
         <v>0.70130000000000003</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="141">
+    <row r="76" spans="6:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q76" s="137">
         <v>12</v>
       </c>
-      <c r="D78" s="141">
+      <c r="R76" s="137">
         <v>42</v>
       </c>
-      <c r="E78" s="143">
+      <c r="S76" s="139">
         <v>0.54700000000000004</v>
       </c>
-      <c r="F78" s="144">
+      <c r="T76" s="140">
         <v>0.5474</v>
       </c>
     </row>
@@ -8101,91 +8462,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="141" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="142" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="142"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="143" t="s">
         <v>150</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
-      <c r="H1" s="87"/>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="88" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="89" t="s">
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="144" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="90" t="s">
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="144" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="90" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
+      <c r="C6" s="144"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="144"/>
+      <c r="G6" s="144"/>
+      <c r="H6" s="144"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="80" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="81" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="81" t="s">
+      <c r="D9" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="E9" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="81" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="H9" s="81" t="s">
         <v>130</v>
-      </c>
-      <c r="E9" s="81" t="s">
-        <v>165</v>
-      </c>
-      <c r="F9" s="81" t="s">
-        <v>163</v>
-      </c>
-      <c r="G9" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="H9" s="81" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="82" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="83">
         <v>157.19999999999999</v>
@@ -8212,7 +8573,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C11" s="83">
         <v>26.2</v>
@@ -8239,7 +8600,7 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="82" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="83">
         <v>0.87</v>
@@ -8266,7 +8627,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="82" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C13" s="83">
         <f>10.75-((300-C10)/100)^1.5</f>
@@ -8295,33 +8656,33 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="81"/>
       <c r="C16" s="81" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="D16" s="81" t="s">
+      <c r="E16" s="81" t="s">
+        <v>164</v>
+      </c>
+      <c r="F16" s="81" t="s">
+        <v>162</v>
+      </c>
+      <c r="G16" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="H16" s="81" t="s">
         <v>130</v>
-      </c>
-      <c r="E16" s="81" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="81" t="s">
-        <v>163</v>
-      </c>
-      <c r="G16" s="81" t="s">
-        <v>164</v>
-      </c>
-      <c r="H16" s="81" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="82" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="85">
         <f>30*C13*C10*C11*(C12+0.7)*0.01</f>
@@ -8344,12 +8705,12 @@
         <v>12228.412612201893</v>
       </c>
       <c r="H17" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="82" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C18" s="85">
         <f>37*C13*C10*C11*(C12+0.7)*0.01</f>
@@ -8372,12 +8733,12 @@
         <v>15081.70888838234</v>
       </c>
       <c r="H18" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C19" s="85">
         <f>C17/1000</f>
@@ -8403,7 +8764,7 @@
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="82" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C20" s="85">
         <f>C18/1000</f>
@@ -8427,19 +8788,19 @@
       </c>
       <c r="H20" s="79"/>
       <c r="L20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="90" t="s">
-        <v>161</v>
-      </c>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="90"/>
+      <c r="B22" s="144" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="144"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="144"/>
+      <c r="H22" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="6">
